--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -19968,6 +19968,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="853">
+      <c r="A853" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B853" t="n">
+        <v>4891</v>
+      </c>
+      <c r="C853" t="n">
+        <v>7.46000003814697</v>
+      </c>
+      <c r="D853" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="E853" t="n">
+        <v>7.19999980926514</v>
+      </c>
+      <c r="F853" t="n">
+        <v>7.46000003814697</v>
+      </c>
+      <c r="G853" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -19991,6 +19991,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="854">
+      <c r="A854" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B854" t="n">
+        <v>2673</v>
+      </c>
+      <c r="C854" t="n">
+        <v>7.42000007629395</v>
+      </c>
+      <c r="D854" t="n">
+        <v>7.23999977111816</v>
+      </c>
+      <c r="E854" t="n">
+        <v>7.42000007629395</v>
+      </c>
+      <c r="F854" t="n">
+        <v>7.40000009536743</v>
+      </c>
+      <c r="G854" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -20014,6 +20014,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="855">
+      <c r="A855" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B855" t="n">
+        <v>8562</v>
+      </c>
+      <c r="C855" t="n">
+        <v>7.53999996185303</v>
+      </c>
+      <c r="D855" t="n">
+        <v>7.28000020980835</v>
+      </c>
+      <c r="E855" t="n">
+        <v>7.44000005722046</v>
+      </c>
+      <c r="F855" t="n">
+        <v>7.53999996185303</v>
+      </c>
+      <c r="G855" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -20037,6 +20037,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="856">
+      <c r="A856" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B856" t="n">
+        <v>8170</v>
+      </c>
+      <c r="C856" t="n">
+        <v>7.51999998092651</v>
+      </c>
+      <c r="D856" t="n">
+        <v>7.40000009536743</v>
+      </c>
+      <c r="E856" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F856" t="n">
+        <v>7.44000005722046</v>
+      </c>
+      <c r="G856" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -19878,22 +19878,22 @@
     </row>
     <row r="849">
       <c r="A849" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B849" t="n">
-        <v>1374</v>
+        <v>11088</v>
       </c>
       <c r="C849" t="n">
-        <v>7.19999980926514</v>
+        <v>7.38000011444092</v>
       </c>
       <c r="D849" t="n">
-        <v>7.15999984741211</v>
+        <v>7.09999990463257</v>
       </c>
       <c r="E849" t="n">
         <v>7.19999980926514</v>
       </c>
       <c r="F849" t="n">
-        <v>7.19999980926514</v>
+        <v>7.26000022888184</v>
       </c>
       <c r="G849" t="s">
         <v>7</v>
@@ -19901,22 +19901,22 @@
     </row>
     <row r="850">
       <c r="A850" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B850" t="n">
-        <v>8247</v>
+        <v>1374</v>
       </c>
       <c r="C850" t="n">
-        <v>7.40000009536743</v>
+        <v>7.19999980926514</v>
       </c>
       <c r="D850" t="n">
-        <v>7.09999990463257</v>
+        <v>7.15999984741211</v>
       </c>
       <c r="E850" t="n">
         <v>7.19999980926514</v>
       </c>
       <c r="F850" t="n">
-        <v>7.23999977111816</v>
+        <v>7.19999980926514</v>
       </c>
       <c r="G850" t="s">
         <v>7</v>
@@ -19924,22 +19924,22 @@
     </row>
     <row r="851">
       <c r="A851" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B851" t="n">
-        <v>20160</v>
+        <v>8247</v>
       </c>
       <c r="C851" t="n">
+        <v>7.40000009536743</v>
+      </c>
+      <c r="D851" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="E851" t="n">
+        <v>7.19999980926514</v>
+      </c>
+      <c r="F851" t="n">
         <v>7.23999977111816</v>
-      </c>
-      <c r="D851" t="n">
-        <v>7.01999998092651</v>
-      </c>
-      <c r="E851" t="n">
-        <v>7.21999979019165</v>
-      </c>
-      <c r="F851" t="n">
-        <v>7.05999994277954</v>
       </c>
       <c r="G851" t="s">
         <v>7</v>
@@ -19947,22 +19947,22 @@
     </row>
     <row r="852">
       <c r="A852" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B852" t="n">
-        <v>5084</v>
+        <v>20160</v>
       </c>
       <c r="C852" t="n">
-        <v>7.19999980926514</v>
+        <v>7.23999977111816</v>
       </c>
       <c r="D852" t="n">
+        <v>7.01999998092651</v>
+      </c>
+      <c r="E852" t="n">
+        <v>7.21999979019165</v>
+      </c>
+      <c r="F852" t="n">
         <v>7.05999994277954</v>
-      </c>
-      <c r="E852" t="n">
-        <v>7.09999990463257</v>
-      </c>
-      <c r="F852" t="n">
-        <v>7.19999980926514</v>
       </c>
       <c r="G852" t="s">
         <v>7</v>
@@ -19970,22 +19970,22 @@
     </row>
     <row r="853">
       <c r="A853" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B853" t="n">
-        <v>4891</v>
+        <v>5084</v>
       </c>
       <c r="C853" t="n">
-        <v>7.46000003814697</v>
+        <v>7.19999980926514</v>
       </c>
       <c r="D853" t="n">
+        <v>7.05999994277954</v>
+      </c>
+      <c r="E853" t="n">
         <v>7.09999990463257</v>
       </c>
-      <c r="E853" t="n">
+      <c r="F853" t="n">
         <v>7.19999980926514</v>
-      </c>
-      <c r="F853" t="n">
-        <v>7.46000003814697</v>
       </c>
       <c r="G853" t="s">
         <v>7</v>
@@ -19993,22 +19993,22 @@
     </row>
     <row r="854">
       <c r="A854" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B854" t="n">
-        <v>2673</v>
+        <v>4891</v>
       </c>
       <c r="C854" t="n">
-        <v>7.42000007629395</v>
+        <v>7.46000003814697</v>
       </c>
       <c r="D854" t="n">
-        <v>7.23999977111816</v>
+        <v>7.09999990463257</v>
       </c>
       <c r="E854" t="n">
-        <v>7.42000007629395</v>
+        <v>7.19999980926514</v>
       </c>
       <c r="F854" t="n">
-        <v>7.40000009536743</v>
+        <v>7.46000003814697</v>
       </c>
       <c r="G854" t="s">
         <v>7</v>
@@ -20016,22 +20016,22 @@
     </row>
     <row r="855">
       <c r="A855" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B855" t="n">
-        <v>8562</v>
+        <v>2673</v>
       </c>
       <c r="C855" t="n">
-        <v>7.53999996185303</v>
+        <v>7.42000007629395</v>
       </c>
       <c r="D855" t="n">
-        <v>7.28000020980835</v>
+        <v>7.23999977111816</v>
       </c>
       <c r="E855" t="n">
-        <v>7.44000005722046</v>
+        <v>7.42000007629395</v>
       </c>
       <c r="F855" t="n">
-        <v>7.53999996185303</v>
+        <v>7.40000009536743</v>
       </c>
       <c r="G855" t="s">
         <v>7</v>
@@ -20039,24 +20039,47 @@
     </row>
     <row r="856">
       <c r="A856" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B856" t="n">
-        <v>8170</v>
+        <v>8562</v>
       </c>
       <c r="C856" t="n">
-        <v>7.51999998092651</v>
+        <v>7.53999996185303</v>
       </c>
       <c r="D856" t="n">
+        <v>7.28000020980835</v>
+      </c>
+      <c r="E856" t="n">
+        <v>7.44000005722046</v>
+      </c>
+      <c r="F856" t="n">
+        <v>7.53999996185303</v>
+      </c>
+      <c r="G856" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B857" t="n">
+        <v>4920</v>
+      </c>
+      <c r="C857" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D857" t="n">
+        <v>7.32000017166138</v>
+      </c>
+      <c r="E857" t="n">
+        <v>7.3600001335144</v>
+      </c>
+      <c r="F857" t="n">
         <v>7.40000009536743</v>
       </c>
-      <c r="E856" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F856" t="n">
-        <v>7.44000005722046</v>
-      </c>
-      <c r="G856" t="s">
+      <c r="G857" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G2" t="n">
-        <v>3.96347832679749</v>
+        <v>3.96347784996033</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G3" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G5" t="n">
-        <v>4.93521928787231</v>
+        <v>4.93521881103516</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G7" t="n">
-        <v>4.64828777313232</v>
+        <v>4.64828729629517</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G8" t="n">
-        <v>4.57177305221558</v>
+        <v>4.57177257537842</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G9" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961290359497</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G10" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961290359497</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961290359497</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961290359497</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961290359497</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961290359497</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>4.59090089797974</v>
+        <v>4.59090137481689</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G18" t="n">
-        <v>4.49525690078735</v>
+        <v>4.49525737762451</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961290359497</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G22" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961290359497</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961290359497</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G24" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961290359497</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G25" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961290359497</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G26" t="n">
-        <v>4.37092018127441</v>
+        <v>4.37092065811157</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G36" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G38" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961290359497</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G42" t="n">
-        <v>4.49525690078735</v>
+        <v>4.49525737762451</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>4.49525690078735</v>
+        <v>4.49525737762451</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>4.49525690078735</v>
+        <v>4.49525737762451</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G45" t="n">
-        <v>4.49525690078735</v>
+        <v>4.49525737762451</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>4.49525690078735</v>
+        <v>4.49525737762451</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G47" t="n">
-        <v>4.49525690078735</v>
+        <v>4.49525737762451</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>4.27521324157715</v>
+        <v>4.27521276473999</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G50" t="n">
-        <v>4.27521324157715</v>
+        <v>4.27521276473999</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G51" t="n">
-        <v>4.37106943130493</v>
+        <v>4.37106990814209</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.75</v>
       </c>
       <c r="G55" t="n">
-        <v>4.55319738388062</v>
+        <v>4.55319786071777</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.75</v>
       </c>
       <c r="G56" t="n">
-        <v>4.55319738388062</v>
+        <v>4.55319786071777</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G57" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.75</v>
       </c>
       <c r="G58" t="n">
-        <v>4.55319738388062</v>
+        <v>4.55319786071777</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.75</v>
       </c>
       <c r="G59" t="n">
-        <v>4.55319738388062</v>
+        <v>4.55319786071777</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G63" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G64" t="n">
-        <v>4.50526857376099</v>
+        <v>4.50526905059814</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>4.50526857376099</v>
+        <v>4.50526905059814</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.75</v>
       </c>
       <c r="G73" t="n">
-        <v>4.55319738388062</v>
+        <v>4.55319786071777</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.75</v>
       </c>
       <c r="G74" t="n">
-        <v>4.55319738388062</v>
+        <v>4.55319786071777</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G78" t="n">
-        <v>4.50526857376099</v>
+        <v>4.50526905059814</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G79" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G81" t="n">
-        <v>4.50526857376099</v>
+        <v>4.50526905059814</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G82" t="n">
-        <v>4.50526857376099</v>
+        <v>4.50526905059814</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G83" t="n">
-        <v>4.50526857376099</v>
+        <v>4.50526905059814</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G90" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G91" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G92" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>4.29438447952271</v>
+        <v>4.29438400268555</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>4.29438447952271</v>
+        <v>4.29438400268555</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>4.29438447952271</v>
+        <v>4.29438400268555</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.29438447952271</v>
+        <v>4.29438400268555</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G97" t="n">
-        <v>4.29438447952271</v>
+        <v>4.29438400268555</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>4.29438447952271</v>
+        <v>4.29438400268555</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>4.29438447952271</v>
+        <v>4.29438400268555</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>4.29438447952271</v>
+        <v>4.29438400268555</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G120" t="n">
-        <v>4.37106943130493</v>
+        <v>4.37106990814209</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>4.37106943130493</v>
+        <v>4.37106990814209</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G122" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G123" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G124" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>4.50526857376099</v>
+        <v>4.50526905059814</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G126" t="n">
-        <v>4.50526857376099</v>
+        <v>4.50526905059814</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>4.50526857376099</v>
+        <v>4.50526905059814</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.50526857376099</v>
+        <v>4.50526905059814</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>3.99722838401794</v>
+        <v>3.99722814559937</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G147" t="n">
-        <v>4.00681352615356</v>
+        <v>4.00681400299072</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>4.00681352615356</v>
+        <v>4.00681400299072</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>4.16977024078369</v>
+        <v>4.16977071762085</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G152" t="n">
-        <v>4.16977024078369</v>
+        <v>4.16977071762085</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G153" t="n">
-        <v>4.16977024078369</v>
+        <v>4.16977071762085</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G154" t="n">
-        <v>4.16977024078369</v>
+        <v>4.16977071762085</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G155" t="n">
-        <v>4.16977024078369</v>
+        <v>4.16977071762085</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G156" t="n">
-        <v>4.16977024078369</v>
+        <v>4.16977071762085</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G157" t="n">
-        <v>4.16977024078369</v>
+        <v>4.16977071762085</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>4.16977024078369</v>
+        <v>4.16977071762085</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G182" t="n">
-        <v>4.76408243179321</v>
+        <v>4.76408195495605</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G185" t="n">
-        <v>4.49568319320679</v>
+        <v>4.49568367004395</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G186" t="n">
-        <v>4.49568319320679</v>
+        <v>4.49568367004395</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G191" t="n">
-        <v>4.64905452728271</v>
+        <v>4.64905405044556</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>4.59154033660889</v>
+        <v>4.59153985977173</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>4.59154033660889</v>
+        <v>4.59153985977173</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G197" t="n">
-        <v>4.44775533676147</v>
+        <v>4.44775485992432</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G200" t="n">
-        <v>4.68739652633667</v>
+        <v>4.68739700317383</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G205" t="n">
-        <v>4.64905452728271</v>
+        <v>4.64905405044556</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>4.64905452728271</v>
+        <v>4.64905405044556</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G215" t="n">
-        <v>4.50526857376099</v>
+        <v>4.50526905059814</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>4.49568319320679</v>
+        <v>4.49568367004395</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G217" t="n">
-        <v>4.50526857376099</v>
+        <v>4.50526905059814</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G218" t="n">
-        <v>4.49568319320679</v>
+        <v>4.49568367004395</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G223" t="n">
-        <v>4.49568319320679</v>
+        <v>4.49568367004395</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>4.50526857376099</v>
+        <v>4.50526905059814</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G225" t="n">
-        <v>4.50526857376099</v>
+        <v>4.50526905059814</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>4.50526857376099</v>
+        <v>4.50526905059814</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G227" t="n">
-        <v>4.50526857376099</v>
+        <v>4.50526905059814</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G229" t="n">
-        <v>4.50526857376099</v>
+        <v>4.50526905059814</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>4.66822528839111</v>
+        <v>4.66822576522827</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G238" t="n">
-        <v>5.9431209564209</v>
+        <v>5.94312047958374</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G239" t="n">
-        <v>5.9431209564209</v>
+        <v>5.94312047958374</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>6</v>
       </c>
       <c r="G240" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>5.8472638130188</v>
+        <v>5.84726428985596</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>5.8472638130188</v>
+        <v>5.84726428985596</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G244" t="n">
-        <v>5.8472638130188</v>
+        <v>5.84726428985596</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G247" t="n">
-        <v>5.9431209564209</v>
+        <v>5.94312047958374</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>6</v>
       </c>
       <c r="G249" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>5.9431209564209</v>
+        <v>5.94312047958374</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>5.8472638130188</v>
+        <v>5.84726428985596</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>6</v>
       </c>
       <c r="G254" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>6</v>
       </c>
       <c r="G257" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>6</v>
       </c>
       <c r="G258" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>6</v>
       </c>
       <c r="G259" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>6</v>
       </c>
       <c r="G260" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>6</v>
       </c>
       <c r="G261" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>6</v>
       </c>
       <c r="G263" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>6</v>
       </c>
       <c r="G264" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>6</v>
       </c>
       <c r="G265" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>6</v>
       </c>
       <c r="G266" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -22706,6 +22706,32 @@
         <v>7.44000005722046</v>
       </c>
       <c r="H859" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B860" t="n">
+        <v>8679</v>
+      </c>
+      <c r="C860" t="n">
+        <v>7.6399998664856</v>
+      </c>
+      <c r="D860" t="n">
+        <v>7.40000009536743</v>
+      </c>
+      <c r="E860" t="n">
+        <v>7.44000005722046</v>
+      </c>
+      <c r="F860" t="n">
+        <v>7.61999988555908</v>
+      </c>
+      <c r="G860" t="n">
+        <v>7.61999988555908</v>
+      </c>
+      <c r="H860" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -473,7 +473,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>4.68654489517212</v>
+        <v>4.68654537200928</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G6" t="n">
-        <v>4.53351449966431</v>
+        <v>4.53351497650146</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G7" t="n">
-        <v>4.64828729629517</v>
+        <v>4.64828777313232</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G9" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G10" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G22" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G24" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G25" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G31" t="n">
-        <v>4.38048505783081</v>
+        <v>4.38048458099365</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G32" t="n">
-        <v>4.45699977874756</v>
+        <v>4.45700025558472</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G33" t="n">
-        <v>4.45699977874756</v>
+        <v>4.45700025558472</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G40" t="n">
-        <v>4.38048505783081</v>
+        <v>4.38048458099365</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>4.38048505783081</v>
+        <v>4.38048458099365</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G51" t="n">
-        <v>4.37106990814209</v>
+        <v>4.37106943130493</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G53" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G54" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.75</v>
       </c>
       <c r="G55" t="n">
-        <v>4.55319786071777</v>
+        <v>4.55319738388062</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.75</v>
       </c>
       <c r="G56" t="n">
-        <v>4.55319786071777</v>
+        <v>4.55319738388062</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G57" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.75</v>
       </c>
       <c r="G58" t="n">
-        <v>4.55319786071777</v>
+        <v>4.55319738388062</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.75</v>
       </c>
       <c r="G59" t="n">
-        <v>4.55319786071777</v>
+        <v>4.55319738388062</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G63" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G66" t="n">
-        <v>4.42858362197876</v>
+        <v>4.42858409881592</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>4.42858362197876</v>
+        <v>4.42858409881592</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>4.42858362197876</v>
+        <v>4.42858409881592</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>4.42858362197876</v>
+        <v>4.42858409881592</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G70" t="n">
-        <v>4.42858362197876</v>
+        <v>4.42858409881592</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G71" t="n">
-        <v>4.42858362197876</v>
+        <v>4.42858409881592</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.75</v>
       </c>
       <c r="G73" t="n">
-        <v>4.55319786071777</v>
+        <v>4.55319738388062</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.75</v>
       </c>
       <c r="G74" t="n">
-        <v>4.55319786071777</v>
+        <v>4.55319738388062</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G79" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G87" t="n">
-        <v>4.39024114608765</v>
+        <v>4.3902416229248</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G88" t="n">
-        <v>4.39024114608765</v>
+        <v>4.3902416229248</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G90" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G91" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G92" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G97" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G115" t="n">
-        <v>4.14101409912109</v>
+        <v>4.14101362228394</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G116" t="n">
-        <v>4.14101409912109</v>
+        <v>4.14101362228394</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G117" t="n">
-        <v>4.14101409912109</v>
+        <v>4.14101362228394</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G120" t="n">
-        <v>4.37106990814209</v>
+        <v>4.37106943130493</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>4.37106990814209</v>
+        <v>4.37106943130493</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G122" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G123" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G124" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G130" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.5</v>
       </c>
       <c r="G131" t="n">
-        <v>4.31355571746826</v>
+        <v>4.3135552406311</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.5</v>
       </c>
       <c r="G132" t="n">
-        <v>4.31355571746826</v>
+        <v>4.3135552406311</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.25</v>
       </c>
       <c r="G142" t="n">
-        <v>4.07391405105591</v>
+        <v>4.07391357421875</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.25</v>
       </c>
       <c r="G143" t="n">
-        <v>4.07391405105591</v>
+        <v>4.07391357421875</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G144" t="n">
-        <v>4.08349990844727</v>
+        <v>4.08349943161011</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G145" t="n">
-        <v>4.08349990844727</v>
+        <v>4.08349943161011</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>3.99722814559937</v>
+        <v>3.99722838401794</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G147" t="n">
-        <v>4.00681400299072</v>
+        <v>4.00681352615356</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>4.00681400299072</v>
+        <v>4.00681352615356</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G152" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G153" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G154" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G155" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G156" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G157" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>4.7449107170105</v>
+        <v>4.74491119384766</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G181" t="n">
-        <v>4.7449107170105</v>
+        <v>4.74491119384766</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G182" t="n">
-        <v>4.76408195495605</v>
+        <v>4.76408243179321</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G185" t="n">
-        <v>4.49568367004395</v>
+        <v>4.4956841468811</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G186" t="n">
-        <v>4.49568367004395</v>
+        <v>4.4956841468811</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G192" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>4.59153985977173</v>
+        <v>4.59154033660889</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>4.59153985977173</v>
+        <v>4.59154033660889</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G196" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G202" t="n">
-        <v>4.72573947906494</v>
+        <v>4.7257399559021</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G207" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G212" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G214" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>4.49568367004395</v>
+        <v>4.4956841468811</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G218" t="n">
-        <v>4.49568367004395</v>
+        <v>4.4956841468811</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G219" t="n">
-        <v>4.32314157485962</v>
+        <v>4.32314205169678</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G223" t="n">
-        <v>4.49568367004395</v>
+        <v>4.4956841468811</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G232" t="n">
-        <v>4.7449107170105</v>
+        <v>4.74491119384766</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G233" t="n">
-        <v>5.02289581298828</v>
+        <v>5.02289533615112</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>5.46383714675903</v>
+        <v>5.46383666992188</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>5.55969381332397</v>
+        <v>5.55969429016113</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G236" t="n">
-        <v>5.60762214660645</v>
+        <v>5.6076226234436</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>5.60762214660645</v>
+        <v>5.6076226234436</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G238" t="n">
-        <v>5.94312047958374</v>
+        <v>5.9431209564209</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G239" t="n">
-        <v>5.94312047958374</v>
+        <v>5.9431209564209</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>5.55969381332397</v>
+        <v>5.55969429016113</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G247" t="n">
-        <v>5.94312047958374</v>
+        <v>5.9431209564209</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>5.94312047958374</v>
+        <v>5.9431209564209</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>6.25</v>
       </c>
       <c r="G252" t="n">
-        <v>5.99104928970337</v>
+        <v>5.99104976654053</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>5.70347881317139</v>
+        <v>5.70347929000854</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>5.90632724761963</v>
+        <v>5.90632772445679</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G301" t="n">
-        <v>5.66426467895508</v>
+        <v>5.66426515579224</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G302" t="n">
-        <v>5.66426467895508</v>
+        <v>5.66426515579224</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>5.66426467895508</v>
+        <v>5.66426515579224</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>5.66426467895508</v>
+        <v>5.66426515579224</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G306" t="n">
-        <v>5.61585235595703</v>
+        <v>5.61585283279419</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>5.61585235595703</v>
+        <v>5.61585283279419</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>5.61585235595703</v>
+        <v>5.61585283279419</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.75</v>
       </c>
       <c r="G323" t="n">
-        <v>5.56744003295898</v>
+        <v>5.56743955612183</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>5.61585235595703</v>
+        <v>5.61585283279419</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>5.61585235595703</v>
+        <v>5.61585283279419</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G347" t="n">
-        <v>6.14839029312134</v>
+        <v>6.14838981628418</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G349" t="n">
-        <v>7.45552825927734</v>
+        <v>7.45552778244019</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G358" t="n">
-        <v>8.61742877960205</v>
+        <v>8.61742782592773</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G359" t="n">
-        <v>8.76266574859619</v>
+        <v>8.76266670227051</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.75</v>
       </c>
       <c r="G362" t="n">
-        <v>9.44044208526611</v>
+        <v>9.4404411315918</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G363" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>10.5539293289185</v>
+        <v>10.5539283752441</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G368" t="n">
-        <v>11.8126544952393</v>
+        <v>11.8126554489136</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G371" t="n">
-        <v>11.8126544952393</v>
+        <v>11.8126554489136</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G376" t="n">
-        <v>11.3285293579102</v>
+        <v>11.3285303115845</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>11.2317047119141</v>
+        <v>11.2317056655884</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>10</v>
       </c>
       <c r="G392" t="n">
-        <v>9.68250370025635</v>
+        <v>9.68250465393066</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G396" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G398" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>10</v>
       </c>
       <c r="G400" t="n">
-        <v>9.68250370025635</v>
+        <v>9.68250465393066</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G401" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G402" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G404" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G405" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G414" t="n">
-        <v>9.05314254760742</v>
+        <v>9.05314159393311</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G415" t="n">
-        <v>9.05314254760742</v>
+        <v>9.05314159393311</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.25</v>
       </c>
       <c r="G416" t="n">
-        <v>8.95631694793701</v>
+        <v>8.9563159942627</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G424" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>9.75</v>
       </c>
       <c r="G427" t="n">
-        <v>9.44044208526611</v>
+        <v>9.4404411315918</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>9.10155296325684</v>
+        <v>9.10155391693115</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>7.5</v>
       </c>
       <c r="G440" t="n">
-        <v>7.261878490448</v>
+        <v>7.26187801361084</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.5</v>
       </c>
       <c r="G441" t="n">
-        <v>7.261878490448</v>
+        <v>7.26187801361084</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G442" t="n">
-        <v>6.87457752227783</v>
+        <v>6.87457799911499</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G449" t="n">
-        <v>6.09997797012329</v>
+        <v>6.09997749328613</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G450" t="n">
-        <v>6.14839029312134</v>
+        <v>6.14838981628418</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G451" t="n">
-        <v>6.09997797012329</v>
+        <v>6.09997749328613</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G452" t="n">
-        <v>6.14839029312134</v>
+        <v>6.14838981628418</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G453" t="n">
-        <v>6.09997797012329</v>
+        <v>6.09997749328613</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>5.90632724761963</v>
+        <v>5.90632772445679</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>6.25</v>
       </c>
       <c r="G458" t="n">
-        <v>6.05156469345093</v>
+        <v>6.05156517028809</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G464" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G469" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G470" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G471" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G475" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G490" t="n">
-        <v>6.39045286178589</v>
+        <v>6.39045238494873</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G491" t="n">
-        <v>6.39045286178589</v>
+        <v>6.39045238494873</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G494" t="n">
-        <v>6.39045286178589</v>
+        <v>6.39045238494873</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G496" t="n">
-        <v>6.50664281845093</v>
+        <v>6.50664234161377</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G497" t="n">
-        <v>6.48727750778198</v>
+        <v>6.48727798461914</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G498" t="n">
-        <v>6.48727750778198</v>
+        <v>6.48727798461914</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G499" t="n">
-        <v>6.48727750778198</v>
+        <v>6.48727798461914</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G500" t="n">
-        <v>6.56473827362061</v>
+        <v>6.56473779678345</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G501" t="n">
-        <v>6.56473827362061</v>
+        <v>6.56473779678345</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G502" t="n">
-        <v>6.56473827362061</v>
+        <v>6.56473779678345</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>6.73902273178101</v>
+        <v>6.73902320861816</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G510" t="n">
-        <v>6.48727750778198</v>
+        <v>6.48727798461914</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G511" t="n">
-        <v>6.56473827362061</v>
+        <v>6.56473779678345</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -22732,6 +22732,32 @@
         <v>7.61999988555908</v>
       </c>
       <c r="H860" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B861" t="n">
+        <v>1505</v>
+      </c>
+      <c r="C861" t="n">
+        <v>7.71999979019165</v>
+      </c>
+      <c r="D861" t="n">
+        <v>7.48000001907349</v>
+      </c>
+      <c r="E861" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="F861" t="n">
+        <v>7.67999982833862</v>
+      </c>
+      <c r="G861" t="n">
+        <v>7.67999982833862</v>
+      </c>
+      <c r="H861" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G2" t="n">
-        <v>3.96347784996033</v>
+        <v>3.96347832679749</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3517918586731</v>
+        <v>4.35179233551025</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>4.68654537200928</v>
+        <v>4.68654489517212</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G6" t="n">
-        <v>4.53351497650146</v>
+        <v>4.53351449966431</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G7" t="n">
-        <v>4.64828777313232</v>
+        <v>4.64828824996948</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G8" t="n">
-        <v>4.57177257537842</v>
+        <v>4.57177305221558</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G9" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G10" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G15" t="n">
-        <v>4.48569297790527</v>
+        <v>4.48569345474243</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G16" t="n">
-        <v>4.48569297790527</v>
+        <v>4.48569345474243</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>4.59090137481689</v>
+        <v>4.59090089797974</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G19" t="n">
-        <v>4.43787097930908</v>
+        <v>4.43787050247192</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G20" t="n">
-        <v>4.43787097930908</v>
+        <v>4.43787050247192</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G22" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G24" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G25" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G27" t="n">
-        <v>4.43787097930908</v>
+        <v>4.43787050247192</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G28" t="n">
-        <v>4.43787097930908</v>
+        <v>4.43787050247192</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G29" t="n">
-        <v>4.43787097930908</v>
+        <v>4.43787050247192</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G30" t="n">
-        <v>4.43787097930908</v>
+        <v>4.43787050247192</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G31" t="n">
-        <v>4.38048458099365</v>
+        <v>4.38048505783081</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G32" t="n">
-        <v>4.45700025558472</v>
+        <v>4.45699977874756</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G33" t="n">
-        <v>4.45700025558472</v>
+        <v>4.45699977874756</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>4.3517918586731</v>
+        <v>4.35179233551025</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G36" t="n">
-        <v>4.3517918586731</v>
+        <v>4.35179233551025</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>4.3517918586731</v>
+        <v>4.35179233551025</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G38" t="n">
-        <v>4.3517918586731</v>
+        <v>4.35179233551025</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G40" t="n">
-        <v>4.38048458099365</v>
+        <v>4.38048505783081</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>4.38048458099365</v>
+        <v>4.38048505783081</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G51" t="n">
-        <v>4.37106943130493</v>
+        <v>4.37106990814209</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G53" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G54" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G66" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G70" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G71" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G87" t="n">
-        <v>4.3902416229248</v>
+        <v>4.39024114608765</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G88" t="n">
-        <v>4.3902416229248</v>
+        <v>4.39024114608765</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G108" t="n">
-        <v>4.12184238433838</v>
+        <v>4.12184286117554</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G120" t="n">
-        <v>4.37106943130493</v>
+        <v>4.37106990814209</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>4.37106943130493</v>
+        <v>4.37106990814209</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G130" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.5</v>
       </c>
       <c r="G131" t="n">
-        <v>4.3135552406311</v>
+        <v>4.31355571746826</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.5</v>
       </c>
       <c r="G132" t="n">
-        <v>4.3135552406311</v>
+        <v>4.31355571746826</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G144" t="n">
-        <v>4.08349943161011</v>
+        <v>4.08349990844727</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G145" t="n">
-        <v>4.08349943161011</v>
+        <v>4.08349990844727</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>3.99722838401794</v>
+        <v>3.99722790718079</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G159" t="n">
-        <v>4.16018486022949</v>
+        <v>4.16018438339233</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>4.15059900283813</v>
+        <v>4.15059852600098</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G161" t="n">
-        <v>4.15059900283813</v>
+        <v>4.15059852600098</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G162" t="n">
-        <v>4.16018486022949</v>
+        <v>4.16018438339233</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G163" t="n">
-        <v>4.16018486022949</v>
+        <v>4.16018438339233</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G164" t="n">
-        <v>4.16018486022949</v>
+        <v>4.16018438339233</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G165" t="n">
-        <v>4.02598524093628</v>
+        <v>4.02598476409912</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>4.03557109832764</v>
+        <v>4.03557062149048</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>4.16018486022949</v>
+        <v>4.16018438339233</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>4.16018486022949</v>
+        <v>4.16018438339233</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>4.15059900283813</v>
+        <v>4.15059852600098</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G176" t="n">
-        <v>4.16018486022949</v>
+        <v>4.16018438339233</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G177" t="n">
-        <v>4.15059900283813</v>
+        <v>4.15059852600098</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>4.15059900283813</v>
+        <v>4.15059852600098</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>4.15059900283813</v>
+        <v>4.15059852600098</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G185" t="n">
-        <v>4.4956841468811</v>
+        <v>4.49568367004395</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G186" t="n">
-        <v>4.4956841468811</v>
+        <v>4.49568367004395</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G191" t="n">
-        <v>4.64905405044556</v>
+        <v>4.64905452728271</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G192" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G196" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G200" t="n">
-        <v>4.68739700317383</v>
+        <v>4.68739652633667</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G202" t="n">
-        <v>4.7257399559021</v>
+        <v>4.72573947906494</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G204" t="n">
-        <v>4.78325366973877</v>
+        <v>4.78325414657593</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G205" t="n">
-        <v>4.64905405044556</v>
+        <v>4.64905452728271</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G207" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>4.64905405044556</v>
+        <v>4.64905452728271</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G212" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G214" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>4.4956841468811</v>
+        <v>4.49568367004395</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G218" t="n">
-        <v>4.4956841468811</v>
+        <v>4.49568367004395</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G219" t="n">
-        <v>4.32314205169678</v>
+        <v>4.32314109802246</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G221" t="n">
-        <v>4.12184238433838</v>
+        <v>4.12184286117554</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G223" t="n">
-        <v>4.4956841468811</v>
+        <v>4.49568367004395</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G228" t="n">
-        <v>4.24645566940308</v>
+        <v>4.24645614624023</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>4.66822576522827</v>
+        <v>4.66822528839111</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G231" t="n">
-        <v>4.6298828125</v>
+        <v>4.62988328933716</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>5.46383666992188</v>
+        <v>5.46383714675903</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>6</v>
       </c>
       <c r="G240" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>6.038978099823</v>
+        <v>6.03897762298584</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>6</v>
       </c>
       <c r="G249" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>6</v>
       </c>
       <c r="G254" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>6</v>
       </c>
       <c r="G257" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>6</v>
       </c>
       <c r="G258" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>6</v>
       </c>
       <c r="G259" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>6</v>
       </c>
       <c r="G260" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>6</v>
       </c>
       <c r="G261" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>5.70347929000854</v>
+        <v>5.70347881317139</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>6</v>
       </c>
       <c r="G263" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>6</v>
       </c>
       <c r="G264" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>6</v>
       </c>
       <c r="G265" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>6</v>
       </c>
       <c r="G266" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -22758,6 +22758,32 @@
         <v>7.67999982833862</v>
       </c>
       <c r="H861" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B862" t="n">
+        <v>5206</v>
+      </c>
+      <c r="C862" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="D862" t="n">
+        <v>7.34000015258789</v>
+      </c>
+      <c r="E862" t="n">
+        <v>7.48000001907349</v>
+      </c>
+      <c r="F862" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="G862" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="H862" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G2" t="n">
-        <v>3.96347832679749</v>
+        <v>3.96347784996033</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>4.68654489517212</v>
+        <v>4.68654441833496</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G5" t="n">
-        <v>4.93521881103516</v>
+        <v>4.93521928787231</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G6" t="n">
-        <v>4.53351449966431</v>
+        <v>4.53351497650146</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G7" t="n">
-        <v>4.64828824996948</v>
+        <v>4.64828777313232</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G8" t="n">
-        <v>4.57177305221558</v>
+        <v>4.57177257537842</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G15" t="n">
-        <v>4.48569345474243</v>
+        <v>4.48569297790527</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G16" t="n">
-        <v>4.48569345474243</v>
+        <v>4.48569297790527</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G18" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G19" t="n">
-        <v>4.43787050247192</v>
+        <v>4.43787097930908</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G20" t="n">
-        <v>4.43787050247192</v>
+        <v>4.43787097930908</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G27" t="n">
-        <v>4.43787050247192</v>
+        <v>4.43787097930908</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G28" t="n">
-        <v>4.43787050247192</v>
+        <v>4.43787097930908</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G29" t="n">
-        <v>4.43787050247192</v>
+        <v>4.43787097930908</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G30" t="n">
-        <v>4.43787050247192</v>
+        <v>4.43787097930908</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G42" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G45" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G47" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>4.27521276473999</v>
+        <v>4.27521324157715</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G50" t="n">
-        <v>4.27521276473999</v>
+        <v>4.27521324157715</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G51" t="n">
-        <v>4.37106990814209</v>
+        <v>4.37106943130493</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G64" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G78" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G81" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G82" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G83" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G108" t="n">
-        <v>4.12184286117554</v>
+        <v>4.12184238433838</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G115" t="n">
-        <v>4.14101362228394</v>
+        <v>4.14101409912109</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G116" t="n">
-        <v>4.14101362228394</v>
+        <v>4.14101409912109</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G117" t="n">
-        <v>4.14101362228394</v>
+        <v>4.14101409912109</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G120" t="n">
-        <v>4.37106990814209</v>
+        <v>4.37106943130493</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>4.37106990814209</v>
+        <v>4.37106943130493</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G126" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.25</v>
       </c>
       <c r="G142" t="n">
-        <v>4.07391357421875</v>
+        <v>4.07391405105591</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.25</v>
       </c>
       <c r="G143" t="n">
-        <v>4.07391357421875</v>
+        <v>4.07391405105591</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>3.99722790718079</v>
+        <v>3.99722838401794</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G159" t="n">
-        <v>4.16018438339233</v>
+        <v>4.16018486022949</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>4.15059852600098</v>
+        <v>4.15059900283813</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G161" t="n">
-        <v>4.15059852600098</v>
+        <v>4.15059900283813</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G162" t="n">
-        <v>4.16018438339233</v>
+        <v>4.16018486022949</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G163" t="n">
-        <v>4.16018438339233</v>
+        <v>4.16018486022949</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G164" t="n">
-        <v>4.16018438339233</v>
+        <v>4.16018486022949</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G165" t="n">
-        <v>4.02598476409912</v>
+        <v>4.02598524093628</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>4.03557062149048</v>
+        <v>4.03557109832764</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>4.16018438339233</v>
+        <v>4.16018486022949</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>4.16018438339233</v>
+        <v>4.16018486022949</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>4.15059852600098</v>
+        <v>4.15059900283813</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G176" t="n">
-        <v>4.16018438339233</v>
+        <v>4.16018486022949</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G177" t="n">
-        <v>4.15059852600098</v>
+        <v>4.15059900283813</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>4.15059852600098</v>
+        <v>4.15059900283813</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>4.15059852600098</v>
+        <v>4.15059900283813</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>4.74491119384766</v>
+        <v>4.7449107170105</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G181" t="n">
-        <v>4.74491119384766</v>
+        <v>4.7449107170105</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G185" t="n">
-        <v>4.49568367004395</v>
+        <v>4.49568319320679</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G186" t="n">
-        <v>4.49568367004395</v>
+        <v>4.49568319320679</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G197" t="n">
-        <v>4.44775485992432</v>
+        <v>4.44775533676147</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G204" t="n">
-        <v>4.78325414657593</v>
+        <v>4.78325366973877</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G215" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>4.49568367004395</v>
+        <v>4.49568319320679</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G217" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G218" t="n">
-        <v>4.49568367004395</v>
+        <v>4.49568319320679</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G219" t="n">
-        <v>4.32314109802246</v>
+        <v>4.32314157485962</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G221" t="n">
-        <v>4.12184286117554</v>
+        <v>4.12184238433838</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G223" t="n">
-        <v>4.49568367004395</v>
+        <v>4.49568319320679</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G225" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G227" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G228" t="n">
-        <v>4.24645614624023</v>
+        <v>4.24645566940308</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G229" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G231" t="n">
-        <v>4.62988328933716</v>
+        <v>4.6298828125</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G232" t="n">
-        <v>4.74491119384766</v>
+        <v>4.7449107170105</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G233" t="n">
-        <v>5.02289533615112</v>
+        <v>5.02289581298828</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>5.55969429016113</v>
+        <v>5.55969381332397</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G236" t="n">
-        <v>5.6076226234436</v>
+        <v>5.60762214660645</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>5.6076226234436</v>
+        <v>5.60762214660645</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>5.84726428985596</v>
+        <v>5.8472638130188</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>5.55969429016113</v>
+        <v>5.55969381332397</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>5.84726428985596</v>
+        <v>5.8472638130188</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G244" t="n">
-        <v>5.84726428985596</v>
+        <v>5.8472638130188</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>6.03897762298584</v>
+        <v>6.038978099823</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>5.84726428985596</v>
+        <v>5.8472638130188</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>6.25</v>
       </c>
       <c r="G252" t="n">
-        <v>5.99104976654053</v>
+        <v>5.99104928970337</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>5.90632772445679</v>
+        <v>5.90632724761963</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G301" t="n">
-        <v>5.66426515579224</v>
+        <v>5.66426467895508</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G302" t="n">
-        <v>5.66426515579224</v>
+        <v>5.66426467895508</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>5.66426515579224</v>
+        <v>5.66426467895508</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>5.66426515579224</v>
+        <v>5.66426467895508</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G306" t="n">
-        <v>5.61585283279419</v>
+        <v>5.61585235595703</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>5.61585283279419</v>
+        <v>5.61585235595703</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>5.61585283279419</v>
+        <v>5.61585235595703</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.75</v>
       </c>
       <c r="G323" t="n">
-        <v>5.56743955612183</v>
+        <v>5.56744003295898</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>5.61585283279419</v>
+        <v>5.61585235595703</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>5.61585283279419</v>
+        <v>5.61585235595703</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G347" t="n">
-        <v>6.14838981628418</v>
+        <v>6.14839029312134</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G349" t="n">
-        <v>7.45552778244019</v>
+        <v>7.45552825927734</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G358" t="n">
-        <v>8.61742782592773</v>
+        <v>8.61742877960205</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G359" t="n">
-        <v>8.76266670227051</v>
+        <v>8.76266574859619</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.75</v>
       </c>
       <c r="G362" t="n">
-        <v>9.4404411315918</v>
+        <v>9.44044208526611</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G363" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>10.5539283752441</v>
+        <v>10.5539293289185</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G368" t="n">
-        <v>11.8126554489136</v>
+        <v>11.8126544952393</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G371" t="n">
-        <v>11.8126554489136</v>
+        <v>11.8126544952393</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G376" t="n">
-        <v>11.3285303115845</v>
+        <v>11.3285293579102</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>11.2317056655884</v>
+        <v>11.2317047119141</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>10</v>
       </c>
       <c r="G392" t="n">
-        <v>9.68250465393066</v>
+        <v>9.68250370025635</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G396" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G398" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>10</v>
       </c>
       <c r="G400" t="n">
-        <v>9.68250465393066</v>
+        <v>9.68250370025635</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G401" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G402" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G404" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G405" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G414" t="n">
-        <v>9.05314159393311</v>
+        <v>9.05314254760742</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G415" t="n">
-        <v>9.05314159393311</v>
+        <v>9.05314254760742</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.25</v>
       </c>
       <c r="G416" t="n">
-        <v>8.9563159942627</v>
+        <v>8.95631694793701</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G424" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>9.75</v>
       </c>
       <c r="G427" t="n">
-        <v>9.4404411315918</v>
+        <v>9.44044208526611</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>9.10155391693115</v>
+        <v>9.10155296325684</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>7.5</v>
       </c>
       <c r="G440" t="n">
-        <v>7.26187801361084</v>
+        <v>7.261878490448</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.5</v>
       </c>
       <c r="G441" t="n">
-        <v>7.26187801361084</v>
+        <v>7.261878490448</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G442" t="n">
-        <v>6.87457799911499</v>
+        <v>6.87457752227783</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G449" t="n">
-        <v>6.09997749328613</v>
+        <v>6.09997797012329</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G450" t="n">
-        <v>6.14838981628418</v>
+        <v>6.14839029312134</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G451" t="n">
-        <v>6.09997749328613</v>
+        <v>6.09997797012329</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G452" t="n">
-        <v>6.14838981628418</v>
+        <v>6.14839029312134</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G453" t="n">
-        <v>6.09997749328613</v>
+        <v>6.09997797012329</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>5.90632772445679</v>
+        <v>5.90632724761963</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>6.25</v>
       </c>
       <c r="G458" t="n">
-        <v>6.05156517028809</v>
+        <v>6.05156469345093</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G464" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G469" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G470" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G471" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G475" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G490" t="n">
-        <v>6.39045238494873</v>
+        <v>6.39045286178589</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G491" t="n">
-        <v>6.39045238494873</v>
+        <v>6.39045286178589</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G494" t="n">
-        <v>6.39045238494873</v>
+        <v>6.39045286178589</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G496" t="n">
-        <v>6.50664234161377</v>
+        <v>6.50664281845093</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G497" t="n">
-        <v>6.48727798461914</v>
+        <v>6.48727750778198</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G498" t="n">
-        <v>6.48727798461914</v>
+        <v>6.48727750778198</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G499" t="n">
-        <v>6.48727798461914</v>
+        <v>6.48727750778198</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G500" t="n">
-        <v>6.56473779678345</v>
+        <v>6.56473827362061</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G501" t="n">
-        <v>6.56473779678345</v>
+        <v>6.56473827362061</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G502" t="n">
-        <v>6.56473779678345</v>
+        <v>6.56473827362061</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>6.73902320861816</v>
+        <v>6.73902273178101</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G510" t="n">
-        <v>6.48727798461914</v>
+        <v>6.48727750778198</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G511" t="n">
-        <v>6.56473779678345</v>
+        <v>6.56473827362061</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -22784,6 +22784,32 @@
         <v>7.65999984741211</v>
       </c>
       <c r="H862" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B863" t="n">
+        <v>8009</v>
+      </c>
+      <c r="C863" t="n">
+        <v>7.71999979019165</v>
+      </c>
+      <c r="D863" t="n">
+        <v>7.40000009536743</v>
+      </c>
+      <c r="E863" t="n">
+        <v>7.67999982833862</v>
+      </c>
+      <c r="F863" t="n">
+        <v>7.57999992370605</v>
+      </c>
+      <c r="G863" t="n">
+        <v>7.57999992370605</v>
+      </c>
+      <c r="H863" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -447,7 +447,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G3" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>4.68654489517212</v>
+        <v>4.68654537200928</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G6" t="n">
-        <v>4.53351449966431</v>
+        <v>4.53351497650146</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G15" t="n">
-        <v>4.48569345474243</v>
+        <v>4.48569297790527</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G16" t="n">
-        <v>4.48569345474243</v>
+        <v>4.48569297790527</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>4.59090185165405</v>
+        <v>4.59090137481689</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G31" t="n">
-        <v>4.38048553466797</v>
+        <v>4.38048458099365</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G32" t="n">
-        <v>4.45699977874756</v>
+        <v>4.45700025558472</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G33" t="n">
-        <v>4.45699977874756</v>
+        <v>4.45700025558472</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.5</v>
       </c>
       <c r="G34" t="n">
-        <v>4.30396938323975</v>
+        <v>4.3039698600769</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G36" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G38" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G40" t="n">
-        <v>4.38048553466797</v>
+        <v>4.38048458099365</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>4.38048553466797</v>
+        <v>4.38048458099365</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.5</v>
       </c>
       <c r="G48" t="n">
-        <v>4.30396938323975</v>
+        <v>4.3039698600769</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -22862,6 +22862,32 @@
         <v>7.55999994277954</v>
       </c>
       <c r="H865" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B866" t="n">
+        <v>2614</v>
+      </c>
+      <c r="C866" t="n">
+        <v>7.78000020980835</v>
+      </c>
+      <c r="D866" t="n">
+        <v>7.40000009536743</v>
+      </c>
+      <c r="E866" t="n">
+        <v>7.53999996185303</v>
+      </c>
+      <c r="F866" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G866" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="H866" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -20352,8 +20352,31 @@
       <c r="E869" t="n">
         <v>7.73999977111816</v>
       </c>
-      <c r="F869"/>
+      <c r="F869" t="n">
+        <v>7.65999984741211</v>
+      </c>
       <c r="G869" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B870" t="n">
+        <v>3301</v>
+      </c>
+      <c r="C870" t="n">
+        <v>7.71999979019165</v>
+      </c>
+      <c r="D870" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="E870" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="F870"/>
+      <c r="G870" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -20375,8 +20375,31 @@
       <c r="E870" t="n">
         <v>7.65999984741211</v>
       </c>
-      <c r="F870"/>
+      <c r="F870" t="n">
+        <v>7.69999980926514</v>
+      </c>
       <c r="G870" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B871" t="n">
+        <v>6678</v>
+      </c>
+      <c r="C871" t="n">
+        <v>7.8600001335144</v>
+      </c>
+      <c r="D871" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E871" t="n">
+        <v>7.6399998664856</v>
+      </c>
+      <c r="F871"/>
+      <c r="G871" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -20398,8 +20398,31 @@
       <c r="E871" t="n">
         <v>7.6399998664856</v>
       </c>
-      <c r="F871"/>
+      <c r="F871" t="n">
+        <v>7.65999984741211</v>
+      </c>
       <c r="G871" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B872" t="n">
+        <v>1252</v>
+      </c>
+      <c r="C872" t="n">
+        <v>7.6399998664856</v>
+      </c>
+      <c r="D872" t="n">
+        <v>7.55999994277954</v>
+      </c>
+      <c r="E872" t="n">
+        <v>7.55999994277954</v>
+      </c>
+      <c r="F872"/>
+      <c r="G872" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -20421,8 +20421,31 @@
       <c r="E872" t="n">
         <v>7.55999994277954</v>
       </c>
-      <c r="F872"/>
+      <c r="F872" t="n">
+        <v>7.6399998664856</v>
+      </c>
       <c r="G872" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B873" t="n">
+        <v>2130</v>
+      </c>
+      <c r="C873" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="D873" t="n">
+        <v>7.53999996185303</v>
+      </c>
+      <c r="E873" t="n">
+        <v>7.55999994277954</v>
+      </c>
+      <c r="F873"/>
+      <c r="G873" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -20451,6 +20451,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="874">
+      <c r="A874" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B874" t="n">
+        <v>2202</v>
+      </c>
+      <c r="C874" t="n">
+        <v>7.76000022888184</v>
+      </c>
+      <c r="D874" t="n">
+        <v>7.6399998664856</v>
+      </c>
+      <c r="E874" t="n">
+        <v>7.6399998664856</v>
+      </c>
+      <c r="F874" t="n">
+        <v>7.76000022888184</v>
+      </c>
+      <c r="G874" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G2" t="n">
-        <v>3.96347784996033</v>
+        <v>3.96347761154175</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>4.68654537200928</v>
+        <v>4.68654441833496</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G5" t="n">
-        <v>4.93521881103516</v>
+        <v>4.93521928787231</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G9" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G10" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>4.59090185165405</v>
+        <v>4.59090137481689</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G22" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G24" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G25" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.5</v>
       </c>
       <c r="G34" t="n">
-        <v>4.30396938323975</v>
+        <v>4.3039698600769</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.5</v>
       </c>
       <c r="G48" t="n">
-        <v>4.30396938323975</v>
+        <v>4.3039698600769</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G51" t="n">
-        <v>4.37106943130493</v>
+        <v>4.37106990814209</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G53" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G54" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.75</v>
       </c>
       <c r="G55" t="n">
-        <v>4.55319738388062</v>
+        <v>4.55319786071777</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.75</v>
       </c>
       <c r="G56" t="n">
-        <v>4.55319738388062</v>
+        <v>4.55319786071777</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G57" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.75</v>
       </c>
       <c r="G58" t="n">
-        <v>4.55319738388062</v>
+        <v>4.55319786071777</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.75</v>
       </c>
       <c r="G59" t="n">
-        <v>4.55319738388062</v>
+        <v>4.55319786071777</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G63" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G66" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G70" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G71" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.75</v>
       </c>
       <c r="G73" t="n">
-        <v>4.55319738388062</v>
+        <v>4.55319786071777</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.75</v>
       </c>
       <c r="G74" t="n">
-        <v>4.55319738388062</v>
+        <v>4.55319786071777</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G79" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G87" t="n">
-        <v>4.3902416229248</v>
+        <v>4.39024114608765</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G88" t="n">
-        <v>4.3902416229248</v>
+        <v>4.39024114608765</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G90" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G91" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G92" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>4.29438447952271</v>
+        <v>4.29438400268555</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>4.29438447952271</v>
+        <v>4.29438400268555</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>4.29438447952271</v>
+        <v>4.29438400268555</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.29438447952271</v>
+        <v>4.29438400268555</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G97" t="n">
-        <v>4.29438447952271</v>
+        <v>4.29438400268555</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>4.29438447952271</v>
+        <v>4.29438400268555</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>4.29438447952271</v>
+        <v>4.29438400268555</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>4.29438447952271</v>
+        <v>4.29438400268555</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G115" t="n">
-        <v>4.14101362228394</v>
+        <v>4.14101409912109</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G116" t="n">
-        <v>4.14101362228394</v>
+        <v>4.14101409912109</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G117" t="n">
-        <v>4.14101362228394</v>
+        <v>4.14101409912109</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G120" t="n">
-        <v>4.37106943130493</v>
+        <v>4.37106990814209</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>4.37106943130493</v>
+        <v>4.37106990814209</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G122" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G123" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G124" t="n">
-        <v>4.4094123840332</v>
+        <v>4.40941190719604</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G130" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.5</v>
       </c>
       <c r="G131" t="n">
-        <v>4.3135552406311</v>
+        <v>4.31355571746826</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.5</v>
       </c>
       <c r="G132" t="n">
-        <v>4.3135552406311</v>
+        <v>4.31355571746826</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.25</v>
       </c>
       <c r="G142" t="n">
-        <v>4.07391357421875</v>
+        <v>4.07391405105591</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.25</v>
       </c>
       <c r="G143" t="n">
-        <v>4.07391357421875</v>
+        <v>4.07391405105591</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G144" t="n">
-        <v>4.08349943161011</v>
+        <v>4.08349990844727</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G145" t="n">
-        <v>4.08349943161011</v>
+        <v>4.08349990844727</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>3.99722838401794</v>
+        <v>3.99722814559937</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G147" t="n">
-        <v>4.00681352615356</v>
+        <v>4.00681400299072</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>4.00681352615356</v>
+        <v>4.00681400299072</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>4.16977024078369</v>
+        <v>4.16977071762085</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G152" t="n">
-        <v>4.16977024078369</v>
+        <v>4.16977071762085</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G153" t="n">
-        <v>4.16977024078369</v>
+        <v>4.16977071762085</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G154" t="n">
-        <v>4.16977024078369</v>
+        <v>4.16977071762085</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G155" t="n">
-        <v>4.16977024078369</v>
+        <v>4.16977071762085</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G156" t="n">
-        <v>4.16977024078369</v>
+        <v>4.16977071762085</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G157" t="n">
-        <v>4.16977024078369</v>
+        <v>4.16977071762085</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>4.16977024078369</v>
+        <v>4.16977071762085</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>4.74491119384766</v>
+        <v>4.7449107170105</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G181" t="n">
-        <v>4.74491119384766</v>
+        <v>4.7449107170105</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G182" t="n">
-        <v>4.76408243179321</v>
+        <v>4.76408195495605</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G185" t="n">
-        <v>4.4956841468811</v>
+        <v>4.49568367004395</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G186" t="n">
-        <v>4.4956841468811</v>
+        <v>4.49568367004395</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G192" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>4.59154033660889</v>
+        <v>4.59153985977173</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>4.59154033660889</v>
+        <v>4.59153985977173</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G196" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G202" t="n">
-        <v>4.7257399559021</v>
+        <v>4.72573947906494</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G207" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G212" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G214" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>4.4956841468811</v>
+        <v>4.49568367004395</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G218" t="n">
-        <v>4.4956841468811</v>
+        <v>4.49568367004395</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G219" t="n">
-        <v>4.32314205169678</v>
+        <v>4.32314157485962</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G223" t="n">
-        <v>4.4956841468811</v>
+        <v>4.49568367004395</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G232" t="n">
-        <v>4.74491119384766</v>
+        <v>4.7449107170105</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G233" t="n">
-        <v>5.02289533615112</v>
+        <v>5.02289581298828</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>5.46383666992188</v>
+        <v>5.46383714675903</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>5.55969429016113</v>
+        <v>5.55969381332397</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G236" t="n">
-        <v>5.6076226234436</v>
+        <v>5.60762214660645</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>5.6076226234436</v>
+        <v>5.60762214660645</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G238" t="n">
-        <v>5.9431209564209</v>
+        <v>5.94312047958374</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G239" t="n">
-        <v>5.9431209564209</v>
+        <v>5.94312047958374</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>5.55969429016113</v>
+        <v>5.55969381332397</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G247" t="n">
-        <v>5.9431209564209</v>
+        <v>5.94312047958374</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>5.9431209564209</v>
+        <v>5.94312047958374</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>6.25</v>
       </c>
       <c r="G252" t="n">
-        <v>5.99104976654053</v>
+        <v>5.99104928970337</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>5.70347929000854</v>
+        <v>5.70347881317139</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>5.90632772445679</v>
+        <v>5.90632724761963</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G301" t="n">
-        <v>5.66426515579224</v>
+        <v>5.66426467895508</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G302" t="n">
-        <v>5.66426515579224</v>
+        <v>5.66426467895508</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>5.66426515579224</v>
+        <v>5.66426467895508</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>5.66426515579224</v>
+        <v>5.66426467895508</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G306" t="n">
-        <v>5.61585283279419</v>
+        <v>5.61585235595703</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>5.61585283279419</v>
+        <v>5.61585235595703</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>5.61585283279419</v>
+        <v>5.61585235595703</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.75</v>
       </c>
       <c r="G323" t="n">
-        <v>5.56743955612183</v>
+        <v>5.56744003295898</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>5.61585283279419</v>
+        <v>5.61585235595703</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>5.61585283279419</v>
+        <v>5.61585235595703</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G347" t="n">
-        <v>6.14838981628418</v>
+        <v>6.14839029312134</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G349" t="n">
-        <v>7.45552778244019</v>
+        <v>7.45552825927734</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G358" t="n">
-        <v>8.61742782592773</v>
+        <v>8.61742877960205</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G359" t="n">
-        <v>8.76266670227051</v>
+        <v>8.76266574859619</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.75</v>
       </c>
       <c r="G362" t="n">
-        <v>9.4404411315918</v>
+        <v>9.44044208526611</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G363" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>10.5539283752441</v>
+        <v>10.5539293289185</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G368" t="n">
-        <v>11.8126554489136</v>
+        <v>11.8126544952393</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G371" t="n">
-        <v>11.8126554489136</v>
+        <v>11.8126544952393</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G376" t="n">
-        <v>11.3285303115845</v>
+        <v>11.3285293579102</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>11.2317056655884</v>
+        <v>11.2317047119141</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>10</v>
       </c>
       <c r="G392" t="n">
-        <v>9.68250465393066</v>
+        <v>9.68250370025635</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G396" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G398" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>10</v>
       </c>
       <c r="G400" t="n">
-        <v>9.68250465393066</v>
+        <v>9.68250370025635</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G401" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G402" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G404" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G405" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G414" t="n">
-        <v>9.05314159393311</v>
+        <v>9.05314254760742</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G415" t="n">
-        <v>9.05314159393311</v>
+        <v>9.05314254760742</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.25</v>
       </c>
       <c r="G416" t="n">
-        <v>8.9563159942627</v>
+        <v>8.95631694793701</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G424" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>9.75</v>
       </c>
       <c r="G427" t="n">
-        <v>9.4404411315918</v>
+        <v>9.44044208526611</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>9.10155391693115</v>
+        <v>9.10155296325684</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>7.5</v>
       </c>
       <c r="G440" t="n">
-        <v>7.26187801361084</v>
+        <v>7.261878490448</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.5</v>
       </c>
       <c r="G441" t="n">
-        <v>7.26187801361084</v>
+        <v>7.261878490448</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G442" t="n">
-        <v>6.87457799911499</v>
+        <v>6.87457752227783</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G449" t="n">
-        <v>6.09997749328613</v>
+        <v>6.09997797012329</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G450" t="n">
-        <v>6.14838981628418</v>
+        <v>6.14839029312134</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G451" t="n">
-        <v>6.09997749328613</v>
+        <v>6.09997797012329</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G452" t="n">
-        <v>6.14838981628418</v>
+        <v>6.14839029312134</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G453" t="n">
-        <v>6.09997749328613</v>
+        <v>6.09997797012329</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>5.90632772445679</v>
+        <v>5.90632724761963</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>6.25</v>
       </c>
       <c r="G458" t="n">
-        <v>6.05156517028809</v>
+        <v>6.05156469345093</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G464" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G469" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G470" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G471" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G475" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G490" t="n">
-        <v>6.39045238494873</v>
+        <v>6.39045286178589</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G491" t="n">
-        <v>6.39045238494873</v>
+        <v>6.39045286178589</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G494" t="n">
-        <v>6.39045238494873</v>
+        <v>6.39045286178589</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G496" t="n">
-        <v>6.50664234161377</v>
+        <v>6.50664281845093</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G497" t="n">
-        <v>6.48727798461914</v>
+        <v>6.48727750778198</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G498" t="n">
-        <v>6.48727798461914</v>
+        <v>6.48727750778198</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G499" t="n">
-        <v>6.48727798461914</v>
+        <v>6.48727750778198</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G500" t="n">
-        <v>6.56473779678345</v>
+        <v>6.56473827362061</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G501" t="n">
-        <v>6.56473779678345</v>
+        <v>6.56473827362061</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G502" t="n">
-        <v>6.56473779678345</v>
+        <v>6.56473827362061</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>6.73902320861816</v>
+        <v>6.73902273178101</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G510" t="n">
-        <v>6.48727798461914</v>
+        <v>6.48727750778198</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G511" t="n">
-        <v>6.56473779678345</v>
+        <v>6.56473827362061</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -23148,6 +23148,32 @@
         <v>7.78000020980835</v>
       </c>
       <c r="H876" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B877" t="n">
+        <v>3640</v>
+      </c>
+      <c r="C877" t="n">
+        <v>7.8600001335144</v>
+      </c>
+      <c r="D877" t="n">
+        <v>7.55999994277954</v>
+      </c>
+      <c r="E877" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="F877" t="n">
+        <v>7.67999982833862</v>
+      </c>
+      <c r="G877" t="n">
+        <v>7.67999982833862</v>
+      </c>
+      <c r="H877" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G2" t="n">
-        <v>3.96347761154175</v>
+        <v>3.96347784996033</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G3" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>4.68654441833496</v>
+        <v>4.68654537200928</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G5" t="n">
-        <v>4.93521928787231</v>
+        <v>4.93521881103516</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G6" t="n">
-        <v>4.53351449966431</v>
+        <v>4.53351497650146</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G9" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G10" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G19" t="n">
-        <v>4.43787097930908</v>
+        <v>4.43787050247192</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G20" t="n">
-        <v>4.43787097930908</v>
+        <v>4.43787050247192</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G22" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G24" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G25" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G26" t="n">
-        <v>4.37092065811157</v>
+        <v>4.37092113494873</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G27" t="n">
-        <v>4.43787097930908</v>
+        <v>4.43787050247192</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G28" t="n">
-        <v>4.43787097930908</v>
+        <v>4.43787050247192</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G29" t="n">
-        <v>4.43787097930908</v>
+        <v>4.43787050247192</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G30" t="n">
-        <v>4.43787097930908</v>
+        <v>4.43787050247192</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G31" t="n">
-        <v>4.38048505783081</v>
+        <v>4.38048458099365</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G32" t="n">
-        <v>4.45699977874756</v>
+        <v>4.45700025558472</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G33" t="n">
-        <v>4.45699977874756</v>
+        <v>4.45700025558472</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G36" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G38" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G40" t="n">
-        <v>4.38048505783081</v>
+        <v>4.38048458099365</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>4.38048505783081</v>
+        <v>4.38048458099365</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.75</v>
       </c>
       <c r="G55" t="n">
-        <v>4.55319786071777</v>
+        <v>4.55319738388062</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.75</v>
       </c>
       <c r="G56" t="n">
-        <v>4.55319786071777</v>
+        <v>4.55319738388062</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G57" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.75</v>
       </c>
       <c r="G58" t="n">
-        <v>4.55319786071777</v>
+        <v>4.55319738388062</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.75</v>
       </c>
       <c r="G59" t="n">
-        <v>4.55319786071777</v>
+        <v>4.55319738388062</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G63" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G72" t="n">
-        <v>4.54361152648926</v>
+        <v>4.54361200332642</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.75</v>
       </c>
       <c r="G73" t="n">
-        <v>4.55319786071777</v>
+        <v>4.55319738388062</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.75</v>
       </c>
       <c r="G74" t="n">
-        <v>4.55319786071777</v>
+        <v>4.55319738388062</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G79" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G90" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G91" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G92" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G97" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G115" t="n">
-        <v>4.14101409912109</v>
+        <v>4.14101362228394</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G116" t="n">
-        <v>4.14101409912109</v>
+        <v>4.14101362228394</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G117" t="n">
-        <v>4.14101409912109</v>
+        <v>4.14101362228394</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G122" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G123" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G124" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G130" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.5</v>
       </c>
       <c r="G131" t="n">
-        <v>4.31355571746826</v>
+        <v>4.3135552406311</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.5</v>
       </c>
       <c r="G132" t="n">
-        <v>4.31355571746826</v>
+        <v>4.3135552406311</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.25</v>
       </c>
       <c r="G142" t="n">
-        <v>4.07391405105591</v>
+        <v>4.07391357421875</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.25</v>
       </c>
       <c r="G143" t="n">
-        <v>4.07391405105591</v>
+        <v>4.07391357421875</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>3.99722814559937</v>
+        <v>3.99722790718079</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G150" t="n">
-        <v>4.23687028884888</v>
+        <v>4.23686981201172</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G152" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G153" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G154" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G155" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G156" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G157" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G165" t="n">
-        <v>4.02598524093628</v>
+        <v>4.02598476409912</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>4.7449107170105</v>
+        <v>4.74491119384766</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G181" t="n">
-        <v>4.7449107170105</v>
+        <v>4.74491119384766</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G182" t="n">
-        <v>4.76408195495605</v>
+        <v>4.76408243179321</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G185" t="n">
-        <v>4.49568367004395</v>
+        <v>4.4956841468811</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G186" t="n">
-        <v>4.49568367004395</v>
+        <v>4.4956841468811</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>4.59153985977173</v>
+        <v>4.59154033660889</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>4.59153985977173</v>
+        <v>4.59154033660889</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G196" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G204" t="n">
-        <v>4.78325366973877</v>
+        <v>4.78325414657593</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G209" t="n">
-        <v>4.54361152648926</v>
+        <v>4.54361200332642</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>4.49568367004395</v>
+        <v>4.4956841468811</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G218" t="n">
-        <v>4.49568367004395</v>
+        <v>4.4956841468811</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G220" t="n">
-        <v>4.23687028884888</v>
+        <v>4.23686981201172</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>4.35189819335938</v>
+        <v>4.35189867019653</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G223" t="n">
-        <v>4.49568367004395</v>
+        <v>4.4956841468811</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G228" t="n">
-        <v>4.24645566940308</v>
+        <v>4.24645614624023</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>4.66822576522827</v>
+        <v>4.66822528839111</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G232" t="n">
-        <v>4.7449107170105</v>
+        <v>4.74491119384766</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G233" t="n">
-        <v>5.02289581298828</v>
+        <v>5.02289533615112</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>5.55969381332397</v>
+        <v>5.55969476699829</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G236" t="n">
-        <v>5.60762214660645</v>
+        <v>5.6076226234436</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>5.60762214660645</v>
+        <v>5.6076226234436</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G238" t="n">
-        <v>5.94312047958374</v>
+        <v>5.9431209564209</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G239" t="n">
-        <v>5.94312047958374</v>
+        <v>5.9431209564209</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>5.84726428985596</v>
+        <v>5.84726476669312</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>5.55969381332397</v>
+        <v>5.55969476699829</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>5.84726428985596</v>
+        <v>5.84726476669312</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G244" t="n">
-        <v>5.84726428985596</v>
+        <v>5.84726476669312</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G247" t="n">
-        <v>5.94312047958374</v>
+        <v>5.9431209564209</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>5.94312047958374</v>
+        <v>5.9431209564209</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>5.84726428985596</v>
+        <v>5.84726476669312</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>6.25</v>
       </c>
       <c r="G252" t="n">
-        <v>5.99104928970337</v>
+        <v>5.99104976654053</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>5.70347881317139</v>
+        <v>5.70347929000854</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>5.90632724761963</v>
+        <v>5.90632772445679</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G301" t="n">
-        <v>5.66426467895508</v>
+        <v>5.66426515579224</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G302" t="n">
-        <v>5.66426467895508</v>
+        <v>5.66426515579224</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>5.66426467895508</v>
+        <v>5.66426515579224</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>5.66426467895508</v>
+        <v>5.66426515579224</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G306" t="n">
-        <v>5.61585235595703</v>
+        <v>5.61585283279419</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>5.61585235595703</v>
+        <v>5.61585283279419</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>5.61585235595703</v>
+        <v>5.61585283279419</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.75</v>
       </c>
       <c r="G323" t="n">
-        <v>5.56744003295898</v>
+        <v>5.56743955612183</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>5.61585235595703</v>
+        <v>5.61585283279419</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>5.61585235595703</v>
+        <v>5.61585283279419</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G347" t="n">
-        <v>6.14839029312134</v>
+        <v>6.14838981628418</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G349" t="n">
-        <v>7.45552825927734</v>
+        <v>7.45552778244019</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G358" t="n">
-        <v>8.61742877960205</v>
+        <v>8.61742782592773</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G359" t="n">
-        <v>8.76266574859619</v>
+        <v>8.76266670227051</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.75</v>
       </c>
       <c r="G362" t="n">
-        <v>9.44044208526611</v>
+        <v>9.4404411315918</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G363" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>10.5539293289185</v>
+        <v>10.5539283752441</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G368" t="n">
-        <v>11.8126544952393</v>
+        <v>11.8126554489136</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G371" t="n">
-        <v>11.8126544952393</v>
+        <v>11.8126554489136</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G376" t="n">
-        <v>11.3285293579102</v>
+        <v>11.3285303115845</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>11.2317047119141</v>
+        <v>11.2317056655884</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>10</v>
       </c>
       <c r="G392" t="n">
-        <v>9.68250370025635</v>
+        <v>9.68250465393066</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G396" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G398" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>10</v>
       </c>
       <c r="G400" t="n">
-        <v>9.68250370025635</v>
+        <v>9.68250465393066</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G401" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G402" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G404" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G405" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G414" t="n">
-        <v>9.05314254760742</v>
+        <v>9.05314159393311</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G415" t="n">
-        <v>9.05314254760742</v>
+        <v>9.05314159393311</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.25</v>
       </c>
       <c r="G416" t="n">
-        <v>8.95631694793701</v>
+        <v>8.9563159942627</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G424" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>9.75</v>
       </c>
       <c r="G427" t="n">
-        <v>9.44044208526611</v>
+        <v>9.4404411315918</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>9.10155296325684</v>
+        <v>9.10155391693115</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>7.5</v>
       </c>
       <c r="G440" t="n">
-        <v>7.261878490448</v>
+        <v>7.26187801361084</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.5</v>
       </c>
       <c r="G441" t="n">
-        <v>7.261878490448</v>
+        <v>7.26187801361084</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G442" t="n">
-        <v>6.87457752227783</v>
+        <v>6.87457799911499</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G449" t="n">
-        <v>6.09997797012329</v>
+        <v>6.09997749328613</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G450" t="n">
-        <v>6.14839029312134</v>
+        <v>6.14838981628418</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G451" t="n">
-        <v>6.09997797012329</v>
+        <v>6.09997749328613</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G452" t="n">
-        <v>6.14839029312134</v>
+        <v>6.14838981628418</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G453" t="n">
-        <v>6.09997797012329</v>
+        <v>6.09997749328613</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>5.90632724761963</v>
+        <v>5.90632772445679</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>6.25</v>
       </c>
       <c r="G458" t="n">
-        <v>6.05156469345093</v>
+        <v>6.05156517028809</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G464" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G469" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G470" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G471" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G475" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G490" t="n">
-        <v>6.39045286178589</v>
+        <v>6.39045238494873</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G491" t="n">
-        <v>6.39045286178589</v>
+        <v>6.39045238494873</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G494" t="n">
-        <v>6.39045286178589</v>
+        <v>6.39045238494873</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G496" t="n">
-        <v>6.50664281845093</v>
+        <v>6.50664234161377</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G497" t="n">
-        <v>6.48727750778198</v>
+        <v>6.48727798461914</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G498" t="n">
-        <v>6.48727750778198</v>
+        <v>6.48727798461914</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G499" t="n">
-        <v>6.48727750778198</v>
+        <v>6.48727798461914</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G500" t="n">
-        <v>6.56473827362061</v>
+        <v>6.56473779678345</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G501" t="n">
-        <v>6.56473827362061</v>
+        <v>6.56473779678345</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G502" t="n">
-        <v>6.56473827362061</v>
+        <v>6.56473779678345</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>6.73902273178101</v>
+        <v>6.73902320861816</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G510" t="n">
-        <v>6.48727750778198</v>
+        <v>6.48727798461914</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G511" t="n">
-        <v>6.56473827362061</v>
+        <v>6.56473779678345</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -23174,6 +23174,32 @@
         <v>7.67999982833862</v>
       </c>
       <c r="H877" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B878" t="n">
+        <v>2263</v>
+      </c>
+      <c r="C878" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="D878" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="E878" t="n">
+        <v>7.61999988555908</v>
+      </c>
+      <c r="F878" t="n">
+        <v>7.78000020980835</v>
+      </c>
+      <c r="G878" t="n">
+        <v>7.78000020980835</v>
+      </c>
+      <c r="H878" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G2" t="n">
-        <v>3.96347784996033</v>
+        <v>3.96347761154175</v>
       </c>
       <c r="H2" t="n">
         <v>19465</v>
@@ -456,7 +456,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3517918586731</v>
+        <v>4.35179233551025</v>
       </c>
       <c r="H3" t="n">
         <v>12331</v>
@@ -485,7 +485,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>4.68654489517212</v>
+        <v>4.68654441833496</v>
       </c>
       <c r="H4" t="n">
         <v>18223</v>
@@ -514,7 +514,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G5" t="n">
-        <v>4.93521881103516</v>
+        <v>4.93521928787231</v>
       </c>
       <c r="H5" t="n">
         <v>6881</v>
@@ -572,7 +572,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G7" t="n">
-        <v>4.64828729629517</v>
+        <v>4.64828777313232</v>
       </c>
       <c r="H7" t="n">
         <v>6450</v>
@@ -630,7 +630,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G9" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H9" t="n">
         <v>4290</v>
@@ -659,7 +659,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G10" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H11" t="n">
         <v>8925</v>
@@ -717,7 +717,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H12" t="n">
         <v>3</v>
@@ -746,7 +746,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H13" t="n">
         <v>2000</v>
@@ -775,7 +775,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H14" t="n">
         <v>700</v>
@@ -804,7 +804,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G15" t="n">
-        <v>4.48569297790527</v>
+        <v>4.48569345474243</v>
       </c>
       <c r="H15" t="n">
         <v>1050</v>
@@ -833,7 +833,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G16" t="n">
-        <v>4.48569297790527</v>
+        <v>4.48569345474243</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H21" t="n">
         <v>1000</v>
@@ -1007,7 +1007,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G22" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H23" t="n">
         <v>400</v>
@@ -1065,7 +1065,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G24" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G25" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>4.3517918586731</v>
+        <v>4.35179233551025</v>
       </c>
       <c r="H35" t="n">
         <v>2300</v>
@@ -1413,7 +1413,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G36" t="n">
-        <v>4.3517918586731</v>
+        <v>4.35179233551025</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>4.3517918586731</v>
+        <v>4.35179233551025</v>
       </c>
       <c r="H37" t="n">
         <v>9</v>
@@ -1471,7 +1471,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G38" t="n">
-        <v>4.3517918586731</v>
+        <v>4.35179233551025</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>4.39961290359497</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H39" t="n">
         <v>1250</v>
@@ -25837,6 +25837,64 @@
         <v>2263</v>
       </c>
       <c r="I878" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="s">
+        <v>9</v>
+      </c>
+      <c r="B879" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C879" t="n">
+        <v>7.78000020980835</v>
+      </c>
+      <c r="D879" t="n">
+        <v>7.78000020980835</v>
+      </c>
+      <c r="E879" t="n">
+        <v>7.51999998092651</v>
+      </c>
+      <c r="F879" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="G879" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="H879" t="n">
+        <v>3145</v>
+      </c>
+      <c r="I879" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="s">
+        <v>9</v>
+      </c>
+      <c r="B880" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C880" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="D880" t="n">
+        <v>7.8600001335144</v>
+      </c>
+      <c r="E880" t="n">
+        <v>7.42000007629395</v>
+      </c>
+      <c r="F880" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G880" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H880" t="n">
+        <v>3422</v>
+      </c>
+      <c r="I880" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -485,7 +485,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>4.68654441833496</v>
+        <v>4.68654489517212</v>
       </c>
       <c r="H4" t="n">
         <v>18223</v>
@@ -514,7 +514,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G5" t="n">
-        <v>4.93521928787231</v>
+        <v>4.93521881103516</v>
       </c>
       <c r="H5" t="n">
         <v>6881</v>
@@ -572,7 +572,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G7" t="n">
-        <v>4.64828777313232</v>
+        <v>4.64828824996948</v>
       </c>
       <c r="H7" t="n">
         <v>6450</v>
@@ -891,7 +891,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G18" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H18" t="n">
         <v>14980</v>
@@ -1123,7 +1123,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G26" t="n">
-        <v>4.37092065811157</v>
+        <v>4.37092018127441</v>
       </c>
       <c r="H26" t="n">
         <v>2</v>
@@ -1268,7 +1268,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G31" t="n">
-        <v>4.38048505783081</v>
+        <v>4.38048553466797</v>
       </c>
       <c r="H31" t="n">
         <v>200</v>
@@ -1297,7 +1297,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G32" t="n">
-        <v>4.45699977874756</v>
+        <v>4.45700025558472</v>
       </c>
       <c r="H32" t="n">
         <v>2150</v>
@@ -1326,7 +1326,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G33" t="n">
-        <v>4.45699977874756</v>
+        <v>4.45700025558472</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G40" t="n">
-        <v>4.38048505783081</v>
+        <v>4.38048553466797</v>
       </c>
       <c r="H40" t="n">
         <v>828</v>
@@ -1558,7 +1558,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>4.38048505783081</v>
+        <v>4.38048553466797</v>
       </c>
       <c r="H41" t="n">
         <v>200</v>
@@ -1587,7 +1587,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G42" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H42" t="n">
         <v>3345</v>
@@ -1616,7 +1616,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G45" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G47" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>4.75</v>
       </c>
       <c r="G55" t="n">
-        <v>4.55319786071777</v>
+        <v>4.55319738388062</v>
       </c>
       <c r="H55" t="n">
         <v>25</v>
@@ -1993,7 +1993,7 @@
         <v>4.75</v>
       </c>
       <c r="G56" t="n">
-        <v>4.55319786071777</v>
+        <v>4.55319738388062</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>4.75</v>
       </c>
       <c r="G58" t="n">
-        <v>4.55319786071777</v>
+        <v>4.55319738388062</v>
       </c>
       <c r="H58" t="n">
         <v>50</v>
@@ -2080,7 +2080,7 @@
         <v>4.75</v>
       </c>
       <c r="G59" t="n">
-        <v>4.55319786071777</v>
+        <v>4.55319738388062</v>
       </c>
       <c r="H59" t="n">
         <v>4</v>
@@ -2109,7 +2109,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G60" t="n">
-        <v>4.43816947937012</v>
+        <v>4.43816995620728</v>
       </c>
       <c r="H60" t="n">
         <v>900</v>
@@ -2138,7 +2138,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G61" t="n">
-        <v>4.43816947937012</v>
+        <v>4.43816995620728</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>4.75</v>
       </c>
       <c r="G73" t="n">
-        <v>4.55319786071777</v>
+        <v>4.55319738388062</v>
       </c>
       <c r="H73" t="n">
         <v>100</v>
@@ -2515,7 +2515,7 @@
         <v>4.75</v>
       </c>
       <c r="G74" t="n">
-        <v>4.55319786071777</v>
+        <v>4.55319738388062</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>4.43816947937012</v>
+        <v>4.43816995620728</v>
       </c>
       <c r="H84" t="n">
         <v>345</v>
@@ -2834,7 +2834,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G85" t="n">
-        <v>4.43816947937012</v>
+        <v>4.43816995620728</v>
       </c>
       <c r="H85" t="n">
         <v>400</v>
@@ -2863,7 +2863,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G86" t="n">
-        <v>4.43816947937012</v>
+        <v>4.43816995620728</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G87" t="n">
-        <v>4.39024114608765</v>
+        <v>4.3902416229248</v>
       </c>
       <c r="H87" t="n">
         <v>500</v>
@@ -2921,7 +2921,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G88" t="n">
-        <v>4.39024114608765</v>
+        <v>4.3902416229248</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H93" t="n">
         <v>1058</v>
@@ -3095,7 +3095,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G97" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>4.29438400268555</v>
+        <v>4.29438447952271</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G101" t="n">
-        <v>4.21769905090332</v>
+        <v>4.21769857406616</v>
       </c>
       <c r="H101" t="n">
         <v>130</v>
@@ -3327,7 +3327,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G102" t="n">
-        <v>4.21769905090332</v>
+        <v>4.21769857406616</v>
       </c>
       <c r="H102" t="n">
         <v>1120</v>
@@ -3356,7 +3356,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>4.21769905090332</v>
+        <v>4.21769857406616</v>
       </c>
       <c r="H103" t="n">
         <v>100</v>
@@ -3385,7 +3385,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>4.21769905090332</v>
+        <v>4.21769857406616</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G105" t="n">
-        <v>4.21769905090332</v>
+        <v>4.21769857406616</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G106" t="n">
-        <v>4.21769905090332</v>
+        <v>4.21769857406616</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G107" t="n">
-        <v>4.21769905090332</v>
+        <v>4.21769857406616</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>4.21769905090332</v>
+        <v>4.21769857406616</v>
       </c>
       <c r="H109" t="n">
         <v>1000</v>
@@ -3559,7 +3559,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>4.21769905090332</v>
+        <v>4.21769857406616</v>
       </c>
       <c r="H110" t="n">
         <v>790</v>
@@ -3588,7 +3588,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G111" t="n">
-        <v>4.21769905090332</v>
+        <v>4.21769857406616</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G112" t="n">
-        <v>4.21769905090332</v>
+        <v>4.21769857406616</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>4.21769905090332</v>
+        <v>4.21769857406616</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>4.21769905090332</v>
+        <v>4.21769857406616</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G115" t="n">
-        <v>4.14101409912109</v>
+        <v>4.14101362228394</v>
       </c>
       <c r="H115" t="n">
         <v>60</v>
@@ -3733,7 +3733,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G116" t="n">
-        <v>4.14101409912109</v>
+        <v>4.14101362228394</v>
       </c>
       <c r="H116" t="n">
         <v>500</v>
@@ -3762,7 +3762,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G117" t="n">
-        <v>4.14101409912109</v>
+        <v>4.14101362228394</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G118" t="n">
-        <v>4.04515647888184</v>
+        <v>4.04515600204468</v>
       </c>
       <c r="H118" t="n">
         <v>150</v>
@@ -3820,7 +3820,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>4.21769905090332</v>
+        <v>4.21769857406616</v>
       </c>
       <c r="H119" t="n">
         <v>832</v>
@@ -4168,7 +4168,7 @@
         <v>4.5</v>
       </c>
       <c r="G131" t="n">
-        <v>4.31355571746826</v>
+        <v>4.3135552406311</v>
       </c>
       <c r="H131" t="n">
         <v>840</v>
@@ -4197,7 +4197,7 @@
         <v>4.5</v>
       </c>
       <c r="G132" t="n">
-        <v>4.31355571746826</v>
+        <v>4.3135552406311</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G138" t="n">
-        <v>4.21769905090332</v>
+        <v>4.21769857406616</v>
       </c>
       <c r="H138" t="n">
         <v>350</v>
@@ -4400,7 +4400,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>4.21769905090332</v>
+        <v>4.21769857406616</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>4.21769905090332</v>
+        <v>4.21769857406616</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>4.21769905090332</v>
+        <v>4.21769857406616</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>4.25</v>
       </c>
       <c r="G142" t="n">
-        <v>4.07391405105591</v>
+        <v>4.07391357421875</v>
       </c>
       <c r="H142" t="n">
         <v>2650</v>
@@ -4516,7 +4516,7 @@
         <v>4.25</v>
       </c>
       <c r="G143" t="n">
-        <v>4.07391405105591</v>
+        <v>4.07391357421875</v>
       </c>
       <c r="H143" t="n">
         <v>1000</v>
@@ -4545,7 +4545,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G144" t="n">
-        <v>4.08349990844727</v>
+        <v>4.08349943161011</v>
       </c>
       <c r="H144" t="n">
         <v>100</v>
@@ -4574,7 +4574,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G145" t="n">
-        <v>4.08349990844727</v>
+        <v>4.08349943161011</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G149" t="n">
-        <v>4.21769905090332</v>
+        <v>4.21769857406616</v>
       </c>
       <c r="H149" t="n">
         <v>1458</v>
@@ -4748,7 +4748,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H151" t="n">
         <v>1085</v>
@@ -4777,7 +4777,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G152" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G153" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G154" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G155" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G156" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G157" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>4.16977071762085</v>
+        <v>4.16977024078369</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G182" t="n">
-        <v>4.76408195495605</v>
+        <v>4.76408243179321</v>
       </c>
       <c r="H182" t="n">
         <v>3903</v>
@@ -5966,7 +5966,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>4.59153985977173</v>
+        <v>4.59154033660889</v>
       </c>
       <c r="H193" t="n">
         <v>2600</v>
@@ -5995,7 +5995,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>4.59153985977173</v>
+        <v>4.59154033660889</v>
       </c>
       <c r="H194" t="n">
         <v>1700</v>
@@ -6198,7 +6198,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G201" t="n">
-        <v>4.7353253364563</v>
+        <v>4.73532581329346</v>
       </c>
       <c r="H201" t="n">
         <v>710</v>
@@ -6227,7 +6227,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G202" t="n">
-        <v>4.72573947906494</v>
+        <v>4.7257399559021</v>
       </c>
       <c r="H202" t="n">
         <v>41</v>
@@ -6401,7 +6401,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G208" t="n">
-        <v>4.7353253364563</v>
+        <v>4.73532581329346</v>
       </c>
       <c r="H208" t="n">
         <v>5979</v>
@@ -6720,7 +6720,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G219" t="n">
-        <v>4.32314157485962</v>
+        <v>4.32314205169678</v>
       </c>
       <c r="H219" t="n">
         <v>8285</v>
@@ -7068,7 +7068,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G231" t="n">
-        <v>4.6298828125</v>
+        <v>4.62988328933716</v>
       </c>
       <c r="H231" t="n">
         <v>941</v>
@@ -7126,7 +7126,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G233" t="n">
-        <v>5.02289581298828</v>
+        <v>5.02289533615112</v>
       </c>
       <c r="H233" t="n">
         <v>1155</v>
@@ -7155,7 +7155,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>5.46383714675903</v>
+        <v>5.46383666992188</v>
       </c>
       <c r="H234" t="n">
         <v>14646</v>
@@ -7271,7 +7271,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G238" t="n">
-        <v>5.94312047958374</v>
+        <v>5.9431209564209</v>
       </c>
       <c r="H238" t="n">
         <v>18133</v>
@@ -7300,7 +7300,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G239" t="n">
-        <v>5.94312047958374</v>
+        <v>5.9431209564209</v>
       </c>
       <c r="H239" t="n">
         <v>25869</v>
@@ -7532,7 +7532,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G247" t="n">
-        <v>5.94312047958374</v>
+        <v>5.9431209564209</v>
       </c>
       <c r="H247" t="n">
         <v>1840</v>
@@ -7619,7 +7619,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>5.94312047958374</v>
+        <v>5.9431209564209</v>
       </c>
       <c r="H250" t="n">
         <v>1843</v>
@@ -25895,6 +25895,35 @@
         <v>3422</v>
       </c>
       <c r="I880" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="s">
+        <v>9</v>
+      </c>
+      <c r="B881" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C881" t="n">
+        <v>7.6399998664856</v>
+      </c>
+      <c r="D881" t="n">
+        <v>7.8600001335144</v>
+      </c>
+      <c r="E881" t="n">
+        <v>7.53999996185303</v>
+      </c>
+      <c r="F881" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="G881" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="H881" t="n">
+        <v>1392</v>
+      </c>
+      <c r="I881" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G2" t="n">
-        <v>3.96347761154175</v>
+        <v>3.96347832679749</v>
       </c>
       <c r="H2" t="n">
         <v>19465</v>
@@ -601,7 +601,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G8" t="n">
-        <v>4.57177257537842</v>
+        <v>4.57177305221558</v>
       </c>
       <c r="H8" t="n">
         <v>1861</v>
@@ -630,7 +630,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G9" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H9" t="n">
         <v>4290</v>
@@ -659,7 +659,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G10" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H11" t="n">
         <v>8925</v>
@@ -717,7 +717,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H12" t="n">
         <v>3</v>
@@ -746,7 +746,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H13" t="n">
         <v>2000</v>
@@ -775,7 +775,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H14" t="n">
         <v>700</v>
@@ -862,7 +862,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>4.59090137481689</v>
+        <v>4.59090089797974</v>
       </c>
       <c r="H17" t="n">
         <v>19623</v>
@@ -891,7 +891,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G18" t="n">
-        <v>4.49525690078735</v>
+        <v>4.49525737762451</v>
       </c>
       <c r="H18" t="n">
         <v>14980</v>
@@ -920,7 +920,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G19" t="n">
-        <v>4.43787097930908</v>
+        <v>4.43787050247192</v>
       </c>
       <c r="H19" t="n">
         <v>1170</v>
@@ -949,7 +949,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G20" t="n">
-        <v>4.43787097930908</v>
+        <v>4.43787050247192</v>
       </c>
       <c r="H20" t="n">
         <v>1300</v>
@@ -978,7 +978,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H21" t="n">
         <v>1000</v>
@@ -1007,7 +1007,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G22" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H23" t="n">
         <v>400</v>
@@ -1065,7 +1065,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G24" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G25" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G26" t="n">
-        <v>4.37092018127441</v>
+        <v>4.37092065811157</v>
       </c>
       <c r="H26" t="n">
         <v>2</v>
@@ -1152,7 +1152,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G27" t="n">
-        <v>4.43787097930908</v>
+        <v>4.43787050247192</v>
       </c>
       <c r="H27" t="n">
         <v>100</v>
@@ -1181,7 +1181,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G28" t="n">
-        <v>4.43787097930908</v>
+        <v>4.43787050247192</v>
       </c>
       <c r="H28" t="n">
         <v>1698</v>
@@ -1210,7 +1210,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G29" t="n">
-        <v>4.43787097930908</v>
+        <v>4.43787050247192</v>
       </c>
       <c r="H29" t="n">
         <v>200</v>
@@ -1239,7 +1239,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G30" t="n">
-        <v>4.43787097930908</v>
+        <v>4.43787050247192</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G31" t="n">
-        <v>4.38048553466797</v>
+        <v>4.38048505783081</v>
       </c>
       <c r="H31" t="n">
         <v>200</v>
@@ -1297,7 +1297,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G32" t="n">
-        <v>4.45700025558472</v>
+        <v>4.45699977874756</v>
       </c>
       <c r="H32" t="n">
         <v>2150</v>
@@ -1326,7 +1326,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G33" t="n">
-        <v>4.45700025558472</v>
+        <v>4.45699977874756</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H39" t="n">
         <v>1250</v>
@@ -1529,7 +1529,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G40" t="n">
-        <v>4.38048553466797</v>
+        <v>4.38048505783081</v>
       </c>
       <c r="H40" t="n">
         <v>828</v>
@@ -1558,7 +1558,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>4.38048553466797</v>
+        <v>4.38048505783081</v>
       </c>
       <c r="H41" t="n">
         <v>200</v>
@@ -1587,7 +1587,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G42" t="n">
-        <v>4.49525690078735</v>
+        <v>4.49525737762451</v>
       </c>
       <c r="H42" t="n">
         <v>3345</v>
@@ -1616,7 +1616,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>4.49525690078735</v>
+        <v>4.49525737762451</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>4.49525690078735</v>
+        <v>4.49525737762451</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G45" t="n">
-        <v>4.49525690078735</v>
+        <v>4.49525737762451</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>4.49525690078735</v>
+        <v>4.49525737762451</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G47" t="n">
-        <v>4.49525690078735</v>
+        <v>4.49525737762451</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H52" t="n">
         <v>250</v>
@@ -2022,7 +2022,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G57" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H57" t="n">
         <v>1330</v>
@@ -2109,7 +2109,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G60" t="n">
-        <v>4.43816995620728</v>
+        <v>4.43816947937012</v>
       </c>
       <c r="H60" t="n">
         <v>900</v>
@@ -2138,7 +2138,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G61" t="n">
-        <v>4.43816995620728</v>
+        <v>4.43816947937012</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H62" t="n">
         <v>465</v>
@@ -2196,7 +2196,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G63" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G79" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H79" t="n">
         <v>300</v>
@@ -2805,7 +2805,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>4.43816995620728</v>
+        <v>4.43816947937012</v>
       </c>
       <c r="H84" t="n">
         <v>345</v>
@@ -2834,7 +2834,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G85" t="n">
-        <v>4.43816995620728</v>
+        <v>4.43816947937012</v>
       </c>
       <c r="H85" t="n">
         <v>400</v>
@@ -2863,7 +2863,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G86" t="n">
-        <v>4.43816995620728</v>
+        <v>4.43816947937012</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G87" t="n">
-        <v>4.3902416229248</v>
+        <v>4.39024114608765</v>
       </c>
       <c r="H87" t="n">
         <v>500</v>
@@ -2921,7 +2921,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G88" t="n">
-        <v>4.3902416229248</v>
+        <v>4.39024114608765</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H89" t="n">
         <v>230</v>
@@ -2979,7 +2979,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G90" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G91" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G92" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G101" t="n">
-        <v>4.21769857406616</v>
+        <v>4.21769905090332</v>
       </c>
       <c r="H101" t="n">
         <v>130</v>
@@ -3327,7 +3327,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G102" t="n">
-        <v>4.21769857406616</v>
+        <v>4.21769905090332</v>
       </c>
       <c r="H102" t="n">
         <v>1120</v>
@@ -3356,7 +3356,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>4.21769857406616</v>
+        <v>4.21769905090332</v>
       </c>
       <c r="H103" t="n">
         <v>100</v>
@@ -3385,7 +3385,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>4.21769857406616</v>
+        <v>4.21769905090332</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G105" t="n">
-        <v>4.21769857406616</v>
+        <v>4.21769905090332</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G106" t="n">
-        <v>4.21769857406616</v>
+        <v>4.21769905090332</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G107" t="n">
-        <v>4.21769857406616</v>
+        <v>4.21769905090332</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G108" t="n">
-        <v>4.12184238433838</v>
+        <v>4.12184286117554</v>
       </c>
       <c r="H108" t="n">
         <v>420</v>
@@ -3530,7 +3530,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>4.21769857406616</v>
+        <v>4.21769905090332</v>
       </c>
       <c r="H109" t="n">
         <v>1000</v>
@@ -3559,7 +3559,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>4.21769857406616</v>
+        <v>4.21769905090332</v>
       </c>
       <c r="H110" t="n">
         <v>790</v>
@@ -3588,7 +3588,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G111" t="n">
-        <v>4.21769857406616</v>
+        <v>4.21769905090332</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G112" t="n">
-        <v>4.21769857406616</v>
+        <v>4.21769905090332</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>4.21769857406616</v>
+        <v>4.21769905090332</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>4.21769857406616</v>
+        <v>4.21769905090332</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G118" t="n">
-        <v>4.04515600204468</v>
+        <v>4.04515647888184</v>
       </c>
       <c r="H118" t="n">
         <v>150</v>
@@ -3820,7 +3820,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>4.21769857406616</v>
+        <v>4.21769905090332</v>
       </c>
       <c r="H119" t="n">
         <v>832</v>
@@ -3907,7 +3907,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G122" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H122" t="n">
         <v>17475</v>
@@ -3936,7 +3936,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G123" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G124" t="n">
-        <v>4.40941190719604</v>
+        <v>4.4094123840332</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>4.5</v>
       </c>
       <c r="G131" t="n">
-        <v>4.3135552406311</v>
+        <v>4.31355571746826</v>
       </c>
       <c r="H131" t="n">
         <v>840</v>
@@ -4197,7 +4197,7 @@
         <v>4.5</v>
       </c>
       <c r="G132" t="n">
-        <v>4.3135552406311</v>
+        <v>4.31355571746826</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G138" t="n">
-        <v>4.21769857406616</v>
+        <v>4.21769905090332</v>
       </c>
       <c r="H138" t="n">
         <v>350</v>
@@ -4400,7 +4400,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>4.21769857406616</v>
+        <v>4.21769905090332</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>4.21769857406616</v>
+        <v>4.21769905090332</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>4.21769857406616</v>
+        <v>4.21769905090332</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G144" t="n">
-        <v>4.08349943161011</v>
+        <v>4.08349990844727</v>
       </c>
       <c r="H144" t="n">
         <v>100</v>
@@ -4574,7 +4574,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G145" t="n">
-        <v>4.08349943161011</v>
+        <v>4.08349990844727</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>3.99722814559937</v>
+        <v>3.99722790718079</v>
       </c>
       <c r="H146" t="n">
         <v>1150</v>
@@ -4632,7 +4632,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G147" t="n">
-        <v>4.00681400299072</v>
+        <v>4.00681352615356</v>
       </c>
       <c r="H147" t="n">
         <v>10</v>
@@ -4661,7 +4661,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>4.00681400299072</v>
+        <v>4.00681352615356</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G149" t="n">
-        <v>4.21769857406616</v>
+        <v>4.21769905090332</v>
       </c>
       <c r="H149" t="n">
         <v>1458</v>
@@ -4980,7 +4980,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G159" t="n">
-        <v>4.16018486022949</v>
+        <v>4.16018438339233</v>
       </c>
       <c r="H159" t="n">
         <v>350</v>
@@ -5009,7 +5009,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>4.15059900283813</v>
+        <v>4.15059852600098</v>
       </c>
       <c r="H160" t="n">
         <v>690</v>
@@ -5038,7 +5038,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G161" t="n">
-        <v>4.15059900283813</v>
+        <v>4.15059852600098</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G162" t="n">
-        <v>4.16018486022949</v>
+        <v>4.16018438339233</v>
       </c>
       <c r="H162" t="n">
         <v>700</v>
@@ -5096,7 +5096,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G163" t="n">
-        <v>4.16018486022949</v>
+        <v>4.16018438339233</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G164" t="n">
-        <v>4.16018486022949</v>
+        <v>4.16018438339233</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G165" t="n">
-        <v>4.02598524093628</v>
+        <v>4.02598476409912</v>
       </c>
       <c r="H165" t="n">
         <v>2701</v>
@@ -5183,7 +5183,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>4.03557109832764</v>
+        <v>4.03557062149048</v>
       </c>
       <c r="H166" t="n">
         <v>266</v>
@@ -5212,7 +5212,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>4.16018486022949</v>
+        <v>4.16018438339233</v>
       </c>
       <c r="H167" t="n">
         <v>410</v>
@@ -5241,7 +5241,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>4.16018486022949</v>
+        <v>4.16018438339233</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>4.15059900283813</v>
+        <v>4.15059852600098</v>
       </c>
       <c r="H169" t="n">
         <v>24</v>
@@ -5473,7 +5473,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G176" t="n">
-        <v>4.16018486022949</v>
+        <v>4.16018438339233</v>
       </c>
       <c r="H176" t="n">
         <v>6468</v>
@@ -5502,7 +5502,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G177" t="n">
-        <v>4.15059900283813</v>
+        <v>4.15059852600098</v>
       </c>
       <c r="H177" t="n">
         <v>791</v>
@@ -5531,7 +5531,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>4.15059900283813</v>
+        <v>4.15059852600098</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>4.15059900283813</v>
+        <v>4.15059852600098</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>4.7449107170105</v>
+        <v>4.74491119384766</v>
       </c>
       <c r="H180" t="n">
         <v>3483</v>
@@ -5618,7 +5618,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G181" t="n">
-        <v>4.7449107170105</v>
+        <v>4.74491119384766</v>
       </c>
       <c r="H181" t="n">
         <v>1342</v>
@@ -5908,7 +5908,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G191" t="n">
-        <v>4.64905405044556</v>
+        <v>4.64905452728271</v>
       </c>
       <c r="H191" t="n">
         <v>2900</v>
@@ -6169,7 +6169,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G200" t="n">
-        <v>4.68739700317383</v>
+        <v>4.68739652633667</v>
       </c>
       <c r="H200" t="n">
         <v>2449</v>
@@ -6198,7 +6198,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G201" t="n">
-        <v>4.73532581329346</v>
+        <v>4.7353253364563</v>
       </c>
       <c r="H201" t="n">
         <v>710</v>
@@ -6227,7 +6227,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G202" t="n">
-        <v>4.7257399559021</v>
+        <v>4.72573947906494</v>
       </c>
       <c r="H202" t="n">
         <v>41</v>
@@ -6285,7 +6285,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G204" t="n">
-        <v>4.78325366973877</v>
+        <v>4.78325414657593</v>
       </c>
       <c r="H204" t="n">
         <v>6987</v>
@@ -6314,7 +6314,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G205" t="n">
-        <v>4.64905405044556</v>
+        <v>4.64905452728271</v>
       </c>
       <c r="H205" t="n">
         <v>6218</v>
@@ -6401,7 +6401,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G208" t="n">
-        <v>4.73532581329346</v>
+        <v>4.7353253364563</v>
       </c>
       <c r="H208" t="n">
         <v>5979</v>
@@ -6488,7 +6488,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>4.64905405044556</v>
+        <v>4.64905452728271</v>
       </c>
       <c r="H211" t="n">
         <v>3534</v>
@@ -6720,7 +6720,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G219" t="n">
-        <v>4.32314205169678</v>
+        <v>4.32314109802246</v>
       </c>
       <c r="H219" t="n">
         <v>8285</v>
@@ -6778,7 +6778,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G221" t="n">
-        <v>4.12184238433838</v>
+        <v>4.12184286117554</v>
       </c>
       <c r="H221" t="n">
         <v>1173</v>
@@ -6981,7 +6981,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G228" t="n">
-        <v>4.24645566940308</v>
+        <v>4.24645614624023</v>
       </c>
       <c r="H228" t="n">
         <v>2110</v>
@@ -7039,7 +7039,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>4.66822576522827</v>
+        <v>4.66822528839111</v>
       </c>
       <c r="H230" t="n">
         <v>3934</v>
@@ -7097,7 +7097,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G232" t="n">
-        <v>4.7449107170105</v>
+        <v>4.74491119384766</v>
       </c>
       <c r="H232" t="n">
         <v>4566</v>
@@ -7155,7 +7155,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>5.46383666992188</v>
+        <v>5.46383714675903</v>
       </c>
       <c r="H234" t="n">
         <v>14646</v>
@@ -7184,7 +7184,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>5.55969381332397</v>
+        <v>5.55969429016113</v>
       </c>
       <c r="H235" t="n">
         <v>6682</v>
@@ -7213,7 +7213,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G236" t="n">
-        <v>5.60762214660645</v>
+        <v>5.6076226234436</v>
       </c>
       <c r="H236" t="n">
         <v>13254</v>
@@ -7242,7 +7242,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>5.60762214660645</v>
+        <v>5.6076226234436</v>
       </c>
       <c r="H237" t="n">
         <v>4716</v>
@@ -7329,7 +7329,7 @@
         <v>6</v>
       </c>
       <c r="G240" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H240" t="n">
         <v>2874</v>
@@ -7387,7 +7387,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>5.55969381332397</v>
+        <v>5.55969429016113</v>
       </c>
       <c r="H242" t="n">
         <v>13513</v>
@@ -7561,7 +7561,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>6.038978099823</v>
+        <v>6.03897762298584</v>
       </c>
       <c r="H248" t="n">
         <v>7527</v>
@@ -7590,7 +7590,7 @@
         <v>6</v>
       </c>
       <c r="G249" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H249" t="n">
         <v>1</v>
@@ -7677,7 +7677,7 @@
         <v>6.25</v>
       </c>
       <c r="G252" t="n">
-        <v>5.99104928970337</v>
+        <v>5.99104976654053</v>
       </c>
       <c r="H252" t="n">
         <v>2848</v>
@@ -7735,7 +7735,7 @@
         <v>6</v>
       </c>
       <c r="G254" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H254" t="n">
         <v>6926</v>
@@ -7822,7 +7822,7 @@
         <v>6</v>
       </c>
       <c r="G257" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H257" t="n">
         <v>180</v>
@@ -7851,7 +7851,7 @@
         <v>6</v>
       </c>
       <c r="G258" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H258" t="n">
         <v>100</v>
@@ -7880,7 +7880,7 @@
         <v>6</v>
       </c>
       <c r="G259" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H259" t="n">
         <v>8795</v>
@@ -7909,7 +7909,7 @@
         <v>6</v>
       </c>
       <c r="G260" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H260" t="n">
         <v>2800</v>
@@ -7938,7 +7938,7 @@
         <v>6</v>
       </c>
       <c r="G261" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H261" t="n">
         <v>5000</v>
@@ -7996,7 +7996,7 @@
         <v>6</v>
       </c>
       <c r="G263" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H263" t="n">
         <v>175</v>
@@ -8025,7 +8025,7 @@
         <v>6</v>
       </c>
       <c r="G264" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H264" t="n">
         <v>300</v>
@@ -8054,7 +8054,7 @@
         <v>6</v>
       </c>
       <c r="G265" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>6</v>
       </c>
       <c r="G266" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H266" t="n">
         <v>50</v>
@@ -9011,7 +9011,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>5.90632724761963</v>
+        <v>5.90632772445679</v>
       </c>
       <c r="H298" t="n">
         <v>6072</v>
@@ -9098,7 +9098,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G301" t="n">
-        <v>5.66426467895508</v>
+        <v>5.66426515579224</v>
       </c>
       <c r="H301" t="n">
         <v>4731</v>
@@ -9127,7 +9127,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G302" t="n">
-        <v>5.66426467895508</v>
+        <v>5.66426515579224</v>
       </c>
       <c r="H302" t="n">
         <v>6123</v>
@@ -9156,7 +9156,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>5.66426467895508</v>
+        <v>5.66426515579224</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>5.66426467895508</v>
+        <v>5.66426515579224</v>
       </c>
       <c r="H305" t="n">
         <v>1</v>
@@ -9243,7 +9243,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G306" t="n">
-        <v>5.61585235595703</v>
+        <v>5.61585283279419</v>
       </c>
       <c r="H306" t="n">
         <v>1509</v>
@@ -9678,7 +9678,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>5.61585235595703</v>
+        <v>5.61585283279419</v>
       </c>
       <c r="H321" t="n">
         <v>2211</v>
@@ -9707,7 +9707,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>5.61585235595703</v>
+        <v>5.61585283279419</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>5.75</v>
       </c>
       <c r="G323" t="n">
-        <v>5.56744003295898</v>
+        <v>5.56743955612183</v>
       </c>
       <c r="H323" t="n">
         <v>1058</v>
@@ -9939,7 +9939,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>5.61585235595703</v>
+        <v>5.61585283279419</v>
       </c>
       <c r="H330" t="n">
         <v>3754</v>
@@ -10374,7 +10374,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>5.61585235595703</v>
+        <v>5.61585283279419</v>
       </c>
       <c r="H345" t="n">
         <v>2400</v>
@@ -10432,7 +10432,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G347" t="n">
-        <v>6.14839029312134</v>
+        <v>6.14838981628418</v>
       </c>
       <c r="H347" t="n">
         <v>37832</v>
@@ -10490,7 +10490,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G349" t="n">
-        <v>7.45552825927734</v>
+        <v>7.45552778244019</v>
       </c>
       <c r="H349" t="n">
         <v>12938</v>
@@ -10751,7 +10751,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G358" t="n">
-        <v>8.61742877960205</v>
+        <v>8.61742782592773</v>
       </c>
       <c r="H358" t="n">
         <v>3309</v>
@@ -10780,7 +10780,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G359" t="n">
-        <v>8.76266574859619</v>
+        <v>8.76266670227051</v>
       </c>
       <c r="H359" t="n">
         <v>4060</v>
@@ -10867,7 +10867,7 @@
         <v>9.75</v>
       </c>
       <c r="G362" t="n">
-        <v>9.44044208526611</v>
+        <v>9.4404411315918</v>
       </c>
       <c r="H362" t="n">
         <v>3792</v>
@@ -10896,7 +10896,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G363" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H363" t="n">
         <v>6251</v>
@@ -10925,7 +10925,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>10.5539293289185</v>
+        <v>10.5539283752441</v>
       </c>
       <c r="H364" t="n">
         <v>5314</v>
@@ -11041,7 +11041,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G368" t="n">
-        <v>11.8126544952393</v>
+        <v>11.8126554489136</v>
       </c>
       <c r="H368" t="n">
         <v>3457</v>
@@ -11128,7 +11128,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G371" t="n">
-        <v>11.8126544952393</v>
+        <v>11.8126554489136</v>
       </c>
       <c r="H371" t="n">
         <v>1348</v>
@@ -11273,7 +11273,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G376" t="n">
-        <v>11.3285293579102</v>
+        <v>11.3285303115845</v>
       </c>
       <c r="H376" t="n">
         <v>1130</v>
@@ -11418,7 +11418,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>11.2317047119141</v>
+        <v>11.2317056655884</v>
       </c>
       <c r="H381" t="n">
         <v>2882</v>
@@ -11737,7 +11737,7 @@
         <v>10</v>
       </c>
       <c r="G392" t="n">
-        <v>9.68250370025635</v>
+        <v>9.68250465393066</v>
       </c>
       <c r="H392" t="n">
         <v>3005</v>
@@ -11853,7 +11853,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G396" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H396" t="n">
         <v>415</v>
@@ -11911,7 +11911,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G398" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H398" t="n">
         <v>12</v>
@@ -11969,7 +11969,7 @@
         <v>10</v>
       </c>
       <c r="G400" t="n">
-        <v>9.68250370025635</v>
+        <v>9.68250465393066</v>
       </c>
       <c r="H400" t="n">
         <v>60</v>
@@ -11998,7 +11998,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G401" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H401" t="n">
         <v>1390</v>
@@ -12027,7 +12027,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G402" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H402" t="n">
         <v>200</v>
@@ -12056,7 +12056,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H403" t="n">
         <v>94</v>
@@ -12085,7 +12085,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G404" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H404" t="n">
         <v>5</v>
@@ -12114,7 +12114,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G405" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H405" t="n">
         <v>126</v>
@@ -12375,7 +12375,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G414" t="n">
-        <v>9.05314254760742</v>
+        <v>9.05314159393311</v>
       </c>
       <c r="H414" t="n">
         <v>1125</v>
@@ -12404,7 +12404,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G415" t="n">
-        <v>9.05314254760742</v>
+        <v>9.05314159393311</v>
       </c>
       <c r="H415" t="n">
         <v>1982</v>
@@ -12433,7 +12433,7 @@
         <v>9.25</v>
       </c>
       <c r="G416" t="n">
-        <v>8.95631694793701</v>
+        <v>8.9563159942627</v>
       </c>
       <c r="H416" t="n">
         <v>71</v>
@@ -12665,7 +12665,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G424" t="n">
-        <v>9.58567810058594</v>
+        <v>9.58567905426025</v>
       </c>
       <c r="H424" t="n">
         <v>1554</v>
@@ -12752,7 +12752,7 @@
         <v>9.75</v>
       </c>
       <c r="G427" t="n">
-        <v>9.44044208526611</v>
+        <v>9.4404411315918</v>
       </c>
       <c r="H427" t="n">
         <v>264</v>
@@ -12897,7 +12897,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>9.10155296325684</v>
+        <v>9.10155391693115</v>
       </c>
       <c r="H432" t="n">
         <v>1636</v>
@@ -13129,7 +13129,7 @@
         <v>7.5</v>
       </c>
       <c r="G440" t="n">
-        <v>7.261878490448</v>
+        <v>7.26187801361084</v>
       </c>
       <c r="H440" t="n">
         <v>3612</v>
@@ -13158,7 +13158,7 @@
         <v>7.5</v>
       </c>
       <c r="G441" t="n">
-        <v>7.261878490448</v>
+        <v>7.26187801361084</v>
       </c>
       <c r="H441" t="n">
         <v>2382</v>
@@ -13187,7 +13187,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G442" t="n">
-        <v>6.87457752227783</v>
+        <v>6.87457799911499</v>
       </c>
       <c r="H442" t="n">
         <v>4692</v>
@@ -13390,7 +13390,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G449" t="n">
-        <v>6.09997797012329</v>
+        <v>6.09997749328613</v>
       </c>
       <c r="H449" t="n">
         <v>15040</v>
@@ -13419,7 +13419,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G450" t="n">
-        <v>6.14839029312134</v>
+        <v>6.14838981628418</v>
       </c>
       <c r="H450" t="n">
         <v>2310</v>
@@ -13448,7 +13448,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G451" t="n">
-        <v>6.09997797012329</v>
+        <v>6.09997749328613</v>
       </c>
       <c r="H451" t="n">
         <v>2158</v>
@@ -13477,7 +13477,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G452" t="n">
-        <v>6.14839029312134</v>
+        <v>6.14838981628418</v>
       </c>
       <c r="H452" t="n">
         <v>2258</v>
@@ -13506,7 +13506,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G453" t="n">
-        <v>6.09997797012329</v>
+        <v>6.09997749328613</v>
       </c>
       <c r="H453" t="n">
         <v>2163</v>
@@ -13535,7 +13535,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>5.90632724761963</v>
+        <v>5.90632772445679</v>
       </c>
       <c r="H454" t="n">
         <v>7331</v>
@@ -13651,7 +13651,7 @@
         <v>6.25</v>
       </c>
       <c r="G458" t="n">
-        <v>6.05156469345093</v>
+        <v>6.05156517028809</v>
       </c>
       <c r="H458" t="n">
         <v>11592</v>
@@ -13825,7 +13825,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G464" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H464" t="n">
         <v>2932</v>
@@ -13854,7 +13854,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H465" t="n">
         <v>2363</v>
@@ -13970,7 +13970,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G469" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H469" t="n">
         <v>9476</v>
@@ -13999,7 +13999,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G470" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H470" t="n">
         <v>2002</v>
@@ -14028,7 +14028,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G471" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H471" t="n">
         <v>2709</v>
@@ -14144,7 +14144,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G475" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H475" t="n">
         <v>1903</v>
@@ -14173,7 +14173,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>6.63251543045044</v>
+        <v>6.63251495361328</v>
       </c>
       <c r="H476" t="n">
         <v>1150</v>
@@ -14579,7 +14579,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G490" t="n">
-        <v>6.39045286178589</v>
+        <v>6.39045238494873</v>
       </c>
       <c r="H490" t="n">
         <v>6956</v>
@@ -14608,7 +14608,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G491" t="n">
-        <v>6.39045286178589</v>
+        <v>6.39045238494873</v>
       </c>
       <c r="H491" t="n">
         <v>25262</v>
@@ -14695,7 +14695,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G494" t="n">
-        <v>6.39045286178589</v>
+        <v>6.39045238494873</v>
       </c>
       <c r="H494" t="n">
         <v>5635</v>
@@ -14753,7 +14753,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G496" t="n">
-        <v>6.50664281845093</v>
+        <v>6.50664234161377</v>
       </c>
       <c r="H496" t="n">
         <v>1359</v>
@@ -14782,7 +14782,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G497" t="n">
-        <v>6.48727750778198</v>
+        <v>6.48727798461914</v>
       </c>
       <c r="H497" t="n">
         <v>200</v>
@@ -14811,7 +14811,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G498" t="n">
-        <v>6.48727750778198</v>
+        <v>6.48727798461914</v>
       </c>
       <c r="H498" t="n">
         <v>14931</v>
@@ -14840,7 +14840,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G499" t="n">
-        <v>6.48727750778198</v>
+        <v>6.48727798461914</v>
       </c>
       <c r="H499" t="n">
         <v>502</v>
@@ -14869,7 +14869,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G500" t="n">
-        <v>6.56473827362061</v>
+        <v>6.56473779678345</v>
       </c>
       <c r="H500" t="n">
         <v>101</v>
@@ -14898,7 +14898,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G501" t="n">
-        <v>6.56473827362061</v>
+        <v>6.56473779678345</v>
       </c>
       <c r="H501" t="n">
         <v>1073</v>
@@ -14927,7 +14927,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G502" t="n">
-        <v>6.56473827362061</v>
+        <v>6.56473779678345</v>
       </c>
       <c r="H502" t="n">
         <v>678</v>
@@ -15014,7 +15014,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>6.73902273178101</v>
+        <v>6.73902320861816</v>
       </c>
       <c r="H505" t="n">
         <v>795</v>
@@ -15159,7 +15159,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G510" t="n">
-        <v>6.48727750778198</v>
+        <v>6.48727798461914</v>
       </c>
       <c r="H510" t="n">
         <v>3139</v>
@@ -15188,7 +15188,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G511" t="n">
-        <v>6.56473827362061</v>
+        <v>6.56473779678345</v>
       </c>
       <c r="H511" t="n">
         <v>2377</v>
@@ -25924,6 +25924,35 @@
         <v>1392</v>
       </c>
       <c r="I881" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="s">
+        <v>9</v>
+      </c>
+      <c r="B882" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C882" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="D882" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="E882" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="F882" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="G882" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="H882" t="n">
+        <v>1002</v>
+      </c>
+      <c r="I882" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -456,7 +456,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G3" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H3" t="n">
         <v>12331</v>
@@ -485,7 +485,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>4.68654489517212</v>
+        <v>4.68654584884644</v>
       </c>
       <c r="H4" t="n">
         <v>18223</v>
@@ -543,7 +543,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G6" t="n">
-        <v>4.53351449966431</v>
+        <v>4.53351497650146</v>
       </c>
       <c r="H6" t="n">
         <v>82495</v>
@@ -572,7 +572,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G7" t="n">
-        <v>4.64828824996948</v>
+        <v>4.64828777313232</v>
       </c>
       <c r="H7" t="n">
         <v>6450</v>
@@ -601,7 +601,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G8" t="n">
-        <v>4.57177305221558</v>
+        <v>4.57177257537842</v>
       </c>
       <c r="H8" t="n">
         <v>1861</v>
@@ -804,7 +804,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G15" t="n">
-        <v>4.48569345474243</v>
+        <v>4.48569297790527</v>
       </c>
       <c r="H15" t="n">
         <v>1050</v>
@@ -833,7 +833,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G16" t="n">
-        <v>4.48569345474243</v>
+        <v>4.48569297790527</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>4.59090089797974</v>
+        <v>4.59090185165405</v>
       </c>
       <c r="H17" t="n">
         <v>19623</v>
@@ -920,7 +920,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G19" t="n">
-        <v>4.43787050247192</v>
+        <v>4.43787097930908</v>
       </c>
       <c r="H19" t="n">
         <v>1170</v>
@@ -949,7 +949,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G20" t="n">
-        <v>4.43787050247192</v>
+        <v>4.43787097930908</v>
       </c>
       <c r="H20" t="n">
         <v>1300</v>
@@ -1152,7 +1152,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G27" t="n">
-        <v>4.43787050247192</v>
+        <v>4.43787097930908</v>
       </c>
       <c r="H27" t="n">
         <v>100</v>
@@ -1181,7 +1181,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G28" t="n">
-        <v>4.43787050247192</v>
+        <v>4.43787097930908</v>
       </c>
       <c r="H28" t="n">
         <v>1698</v>
@@ -1210,7 +1210,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G29" t="n">
-        <v>4.43787050247192</v>
+        <v>4.43787097930908</v>
       </c>
       <c r="H29" t="n">
         <v>200</v>
@@ -1239,7 +1239,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G30" t="n">
-        <v>4.43787050247192</v>
+        <v>4.43787097930908</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G32" t="n">
-        <v>4.45699977874756</v>
+        <v>4.45700025558472</v>
       </c>
       <c r="H32" t="n">
         <v>2150</v>
@@ -1326,7 +1326,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G33" t="n">
-        <v>4.45699977874756</v>
+        <v>4.45700025558472</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H35" t="n">
         <v>2300</v>
@@ -1413,7 +1413,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G36" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H37" t="n">
         <v>9</v>
@@ -1471,7 +1471,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G38" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G51" t="n">
-        <v>4.37106990814209</v>
+        <v>4.37106943130493</v>
       </c>
       <c r="H51" t="n">
         <v>3376</v>
@@ -1906,7 +1906,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G53" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H53" t="n">
         <v>6000</v>
@@ -1935,7 +1935,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G54" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G66" t="n">
-        <v>4.42858362197876</v>
+        <v>4.42858409881592</v>
       </c>
       <c r="H66" t="n">
         <v>350</v>
@@ -2312,7 +2312,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>4.42858362197876</v>
+        <v>4.42858409881592</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>4.42858362197876</v>
+        <v>4.42858409881592</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>4.42858362197876</v>
+        <v>4.42858409881592</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G70" t="n">
-        <v>4.42858362197876</v>
+        <v>4.42858409881592</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G71" t="n">
-        <v>4.42858362197876</v>
+        <v>4.42858409881592</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H75" t="n">
         <v>560</v>
@@ -2573,7 +2573,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G87" t="n">
-        <v>4.39024114608765</v>
+        <v>4.3902416229248</v>
       </c>
       <c r="H87" t="n">
         <v>500</v>
@@ -2921,7 +2921,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G88" t="n">
-        <v>4.39024114608765</v>
+        <v>4.3902416229248</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G108" t="n">
-        <v>4.12184286117554</v>
+        <v>4.12184238433838</v>
       </c>
       <c r="H108" t="n">
         <v>420</v>
@@ -3849,7 +3849,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G120" t="n">
-        <v>4.37106990814209</v>
+        <v>4.37106943130493</v>
       </c>
       <c r="H120" t="n">
         <v>3050</v>
@@ -3878,7 +3878,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>4.37106990814209</v>
+        <v>4.37106943130493</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H129" t="n">
         <v>30</v>
@@ -4139,7 +4139,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G130" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>4.5</v>
       </c>
       <c r="G131" t="n">
-        <v>4.31355571746826</v>
+        <v>4.3135552406311</v>
       </c>
       <c r="H131" t="n">
         <v>840</v>
@@ -4197,7 +4197,7 @@
         <v>4.5</v>
       </c>
       <c r="G132" t="n">
-        <v>4.31355571746826</v>
+        <v>4.3135552406311</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G144" t="n">
-        <v>4.08349990844727</v>
+        <v>4.08349943161011</v>
       </c>
       <c r="H144" t="n">
         <v>100</v>
@@ -4574,7 +4574,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G145" t="n">
-        <v>4.08349990844727</v>
+        <v>4.08349943161011</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>3.99722790718079</v>
+        <v>3.99722838401794</v>
       </c>
       <c r="H146" t="n">
         <v>1150</v>
@@ -4980,7 +4980,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G159" t="n">
-        <v>4.16018438339233</v>
+        <v>4.16018486022949</v>
       </c>
       <c r="H159" t="n">
         <v>350</v>
@@ -5009,7 +5009,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>4.15059852600098</v>
+        <v>4.15059900283813</v>
       </c>
       <c r="H160" t="n">
         <v>690</v>
@@ -5038,7 +5038,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G161" t="n">
-        <v>4.15059852600098</v>
+        <v>4.15059900283813</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G162" t="n">
-        <v>4.16018438339233</v>
+        <v>4.16018486022949</v>
       </c>
       <c r="H162" t="n">
         <v>700</v>
@@ -5096,7 +5096,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G163" t="n">
-        <v>4.16018438339233</v>
+        <v>4.16018486022949</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G164" t="n">
-        <v>4.16018438339233</v>
+        <v>4.16018486022949</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G165" t="n">
-        <v>4.02598476409912</v>
+        <v>4.02598524093628</v>
       </c>
       <c r="H165" t="n">
         <v>2701</v>
@@ -5183,7 +5183,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>4.03557062149048</v>
+        <v>4.03557109832764</v>
       </c>
       <c r="H166" t="n">
         <v>266</v>
@@ -5212,7 +5212,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>4.16018438339233</v>
+        <v>4.16018486022949</v>
       </c>
       <c r="H167" t="n">
         <v>410</v>
@@ -5241,7 +5241,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>4.16018438339233</v>
+        <v>4.16018486022949</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>4.15059852600098</v>
+        <v>4.15059900283813</v>
       </c>
       <c r="H169" t="n">
         <v>24</v>
@@ -5473,7 +5473,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G176" t="n">
-        <v>4.16018438339233</v>
+        <v>4.16018486022949</v>
       </c>
       <c r="H176" t="n">
         <v>6468</v>
@@ -5502,7 +5502,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G177" t="n">
-        <v>4.15059852600098</v>
+        <v>4.15059900283813</v>
       </c>
       <c r="H177" t="n">
         <v>791</v>
@@ -5531,7 +5531,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>4.15059852600098</v>
+        <v>4.15059900283813</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>4.15059852600098</v>
+        <v>4.15059900283813</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H183" t="n">
         <v>5513</v>
@@ -5734,7 +5734,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G185" t="n">
-        <v>4.49568367004395</v>
+        <v>4.4956841468811</v>
       </c>
       <c r="H185" t="n">
         <v>1100</v>
@@ -5763,7 +5763,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G186" t="n">
-        <v>4.49568367004395</v>
+        <v>4.4956841468811</v>
       </c>
       <c r="H186" t="n">
         <v>150</v>
@@ -5908,7 +5908,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G191" t="n">
-        <v>4.64905452728271</v>
+        <v>4.64905405044556</v>
       </c>
       <c r="H191" t="n">
         <v>2900</v>
@@ -5937,7 +5937,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G192" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H192" t="n">
         <v>36</v>
@@ -6024,7 +6024,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H195" t="n">
         <v>858</v>
@@ -6053,7 +6053,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G196" t="n">
-        <v>4.45734119415283</v>
+        <v>4.45734071731567</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H198" t="n">
         <v>5205</v>
@@ -6140,7 +6140,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G200" t="n">
-        <v>4.68739652633667</v>
+        <v>4.68739700317383</v>
       </c>
       <c r="H200" t="n">
         <v>2449</v>
@@ -6227,7 +6227,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G202" t="n">
-        <v>4.72573947906494</v>
+        <v>4.7257399559021</v>
       </c>
       <c r="H202" t="n">
         <v>41</v>
@@ -6285,7 +6285,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G204" t="n">
-        <v>4.78325414657593</v>
+        <v>4.78325366973877</v>
       </c>
       <c r="H204" t="n">
         <v>6987</v>
@@ -6314,7 +6314,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G205" t="n">
-        <v>4.64905452728271</v>
+        <v>4.64905405044556</v>
       </c>
       <c r="H205" t="n">
         <v>6218</v>
@@ -6372,7 +6372,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G207" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H207" t="n">
         <v>716</v>
@@ -6488,7 +6488,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>4.64905452728271</v>
+        <v>4.64905405044556</v>
       </c>
       <c r="H211" t="n">
         <v>3534</v>
@@ -6517,7 +6517,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G212" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H212" t="n">
         <v>13614</v>
@@ -6575,7 +6575,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G214" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H214" t="n">
         <v>304</v>
@@ -6633,7 +6633,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>4.49568367004395</v>
+        <v>4.4956841468811</v>
       </c>
       <c r="H216" t="n">
         <v>3969</v>
@@ -6691,7 +6691,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G218" t="n">
-        <v>4.49568367004395</v>
+        <v>4.4956841468811</v>
       </c>
       <c r="H218" t="n">
         <v>553</v>
@@ -6720,7 +6720,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G219" t="n">
-        <v>4.32314109802246</v>
+        <v>4.32314205169678</v>
       </c>
       <c r="H219" t="n">
         <v>8285</v>
@@ -6778,7 +6778,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G221" t="n">
-        <v>4.12184286117554</v>
+        <v>4.12184238433838</v>
       </c>
       <c r="H221" t="n">
         <v>1173</v>
@@ -6836,7 +6836,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G223" t="n">
-        <v>4.49568367004395</v>
+        <v>4.4956841468811</v>
       </c>
       <c r="H223" t="n">
         <v>3084</v>
@@ -6981,7 +6981,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G228" t="n">
-        <v>4.24645614624023</v>
+        <v>4.24645566940308</v>
       </c>
       <c r="H228" t="n">
         <v>2110</v>
@@ -7039,7 +7039,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>4.66822528839111</v>
+        <v>4.66822576522827</v>
       </c>
       <c r="H230" t="n">
         <v>3934</v>
@@ -7068,7 +7068,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G231" t="n">
-        <v>4.62988328933716</v>
+        <v>4.6298828125</v>
       </c>
       <c r="H231" t="n">
         <v>941</v>
@@ -7155,7 +7155,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>5.46383714675903</v>
+        <v>5.46383666992188</v>
       </c>
       <c r="H234" t="n">
         <v>14646</v>
@@ -7329,7 +7329,7 @@
         <v>6</v>
       </c>
       <c r="G240" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H240" t="n">
         <v>2874</v>
@@ -7561,7 +7561,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>6.03897762298584</v>
+        <v>6.038978099823</v>
       </c>
       <c r="H248" t="n">
         <v>7527</v>
@@ -7590,7 +7590,7 @@
         <v>6</v>
       </c>
       <c r="G249" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H249" t="n">
         <v>1</v>
@@ -7735,7 +7735,7 @@
         <v>6</v>
       </c>
       <c r="G254" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H254" t="n">
         <v>6926</v>
@@ -7822,7 +7822,7 @@
         <v>6</v>
       </c>
       <c r="G257" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H257" t="n">
         <v>180</v>
@@ -7851,7 +7851,7 @@
         <v>6</v>
       </c>
       <c r="G258" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H258" t="n">
         <v>100</v>
@@ -7880,7 +7880,7 @@
         <v>6</v>
       </c>
       <c r="G259" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H259" t="n">
         <v>8795</v>
@@ -7909,7 +7909,7 @@
         <v>6</v>
       </c>
       <c r="G260" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H260" t="n">
         <v>2800</v>
@@ -7938,7 +7938,7 @@
         <v>6</v>
       </c>
       <c r="G261" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H261" t="n">
         <v>5000</v>
@@ -7967,7 +7967,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>5.70347881317139</v>
+        <v>5.70347929000854</v>
       </c>
       <c r="H262" t="n">
         <v>1549</v>
@@ -7996,7 +7996,7 @@
         <v>6</v>
       </c>
       <c r="G263" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H263" t="n">
         <v>175</v>
@@ -8025,7 +8025,7 @@
         <v>6</v>
       </c>
       <c r="G264" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H264" t="n">
         <v>300</v>
@@ -8054,7 +8054,7 @@
         <v>6</v>
       </c>
       <c r="G265" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>6</v>
       </c>
       <c r="G266" t="n">
-        <v>5.75140714645386</v>
+        <v>5.75140762329102</v>
       </c>
       <c r="H266" t="n">
         <v>50</v>
@@ -25953,6 +25953,35 @@
         <v>1002</v>
       </c>
       <c r="I882" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="s">
+        <v>9</v>
+      </c>
+      <c r="B883" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C883" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="D883" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="E883" t="n">
+        <v>7.38000011444092</v>
+      </c>
+      <c r="F883" t="n">
+        <v>7.55999994277954</v>
+      </c>
+      <c r="G883" t="n">
+        <v>7.55999994277954</v>
+      </c>
+      <c r="H883" t="n">
+        <v>1675</v>
+      </c>
+      <c r="I883" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G2" t="n">
-        <v>3.96347832679749</v>
+        <v>3.96347784996033</v>
       </c>
       <c r="H2" t="n">
         <v>19465</v>
@@ -485,7 +485,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>4.68654584884644</v>
+        <v>4.68654537200928</v>
       </c>
       <c r="H4" t="n">
         <v>18223</v>
@@ -601,7 +601,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G8" t="n">
-        <v>4.57177257537842</v>
+        <v>4.57177209854126</v>
       </c>
       <c r="H8" t="n">
         <v>1861</v>
@@ -630,7 +630,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G9" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H9" t="n">
         <v>4290</v>
@@ -659,7 +659,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G10" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H11" t="n">
         <v>8925</v>
@@ -717,7 +717,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H12" t="n">
         <v>3</v>
@@ -746,7 +746,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H13" t="n">
         <v>2000</v>
@@ -775,7 +775,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H14" t="n">
         <v>700</v>
@@ -804,7 +804,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G15" t="n">
-        <v>4.48569297790527</v>
+        <v>4.48569345474243</v>
       </c>
       <c r="H15" t="n">
         <v>1050</v>
@@ -833,7 +833,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G16" t="n">
-        <v>4.48569297790527</v>
+        <v>4.48569345474243</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>4.59090185165405</v>
+        <v>4.59090137481689</v>
       </c>
       <c r="H17" t="n">
         <v>19623</v>
@@ -978,7 +978,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H21" t="n">
         <v>1000</v>
@@ -1007,7 +1007,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G22" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H23" t="n">
         <v>400</v>
@@ -1065,7 +1065,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G24" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G25" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G31" t="n">
-        <v>4.38048505783081</v>
+        <v>4.38048458099365</v>
       </c>
       <c r="H31" t="n">
         <v>200</v>
@@ -1500,7 +1500,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>4.39961385726929</v>
+        <v>4.39961338043213</v>
       </c>
       <c r="H39" t="n">
         <v>1250</v>
@@ -1529,7 +1529,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G40" t="n">
-        <v>4.38048505783081</v>
+        <v>4.38048458099365</v>
       </c>
       <c r="H40" t="n">
         <v>828</v>
@@ -1558,7 +1558,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>4.38048505783081</v>
+        <v>4.38048458099365</v>
       </c>
       <c r="H41" t="n">
         <v>200</v>
@@ -1848,7 +1848,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G51" t="n">
-        <v>4.37106943130493</v>
+        <v>4.37106990814209</v>
       </c>
       <c r="H51" t="n">
         <v>3376</v>
@@ -1906,7 +1906,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G53" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H53" t="n">
         <v>6000</v>
@@ -1935,7 +1935,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G54" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G66" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H66" t="n">
         <v>350</v>
@@ -2312,7 +2312,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G70" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G71" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G72" t="n">
-        <v>4.54361152648926</v>
+        <v>4.54361200332642</v>
       </c>
       <c r="H72" t="n">
         <v>2170</v>
@@ -2892,7 +2892,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G87" t="n">
-        <v>4.3902416229248</v>
+        <v>4.39024114608765</v>
       </c>
       <c r="H87" t="n">
         <v>500</v>
@@ -2921,7 +2921,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G88" t="n">
-        <v>4.3902416229248</v>
+        <v>4.39024114608765</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G120" t="n">
-        <v>4.37106943130493</v>
+        <v>4.37106990814209</v>
       </c>
       <c r="H120" t="n">
         <v>3050</v>
@@ -3878,7 +3878,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>4.37106943130493</v>
+        <v>4.37106990814209</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G144" t="n">
-        <v>4.08349943161011</v>
+        <v>4.08349990844727</v>
       </c>
       <c r="H144" t="n">
         <v>100</v>
@@ -4574,7 +4574,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G145" t="n">
-        <v>4.08349943161011</v>
+        <v>4.08349990844727</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>3.99722838401794</v>
+        <v>3.99722790718079</v>
       </c>
       <c r="H146" t="n">
         <v>1150</v>
@@ -4632,7 +4632,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G147" t="n">
-        <v>4.00681352615356</v>
+        <v>4.00681400299072</v>
       </c>
       <c r="H147" t="n">
         <v>10</v>
@@ -4661,7 +4661,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>4.00681352615356</v>
+        <v>4.00681400299072</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G150" t="n">
-        <v>4.23687028884888</v>
+        <v>4.23686981201172</v>
       </c>
       <c r="H150" t="n">
         <v>1292</v>
@@ -5154,7 +5154,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G165" t="n">
-        <v>4.02598524093628</v>
+        <v>4.02598476409912</v>
       </c>
       <c r="H165" t="n">
         <v>2701</v>
@@ -5676,7 +5676,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H183" t="n">
         <v>5513</v>
@@ -5937,7 +5937,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G192" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H192" t="n">
         <v>36</v>
@@ -6111,7 +6111,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H198" t="n">
         <v>5205</v>
@@ -6140,7 +6140,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G202" t="n">
-        <v>4.7257399559021</v>
+        <v>4.72573947906494</v>
       </c>
       <c r="H202" t="n">
         <v>41</v>
@@ -6285,7 +6285,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G204" t="n">
-        <v>4.78325366973877</v>
+        <v>4.78325414657593</v>
       </c>
       <c r="H204" t="n">
         <v>6987</v>
@@ -6372,7 +6372,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G207" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H207" t="n">
         <v>716</v>
@@ -6430,7 +6430,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G209" t="n">
-        <v>4.54361152648926</v>
+        <v>4.54361200332642</v>
       </c>
       <c r="H209" t="n">
         <v>6246</v>
@@ -6517,7 +6517,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G212" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H212" t="n">
         <v>13614</v>
@@ -6575,7 +6575,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G214" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H214" t="n">
         <v>304</v>
@@ -6720,7 +6720,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G219" t="n">
-        <v>4.32314205169678</v>
+        <v>4.32314157485962</v>
       </c>
       <c r="H219" t="n">
         <v>8285</v>
@@ -6749,7 +6749,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G220" t="n">
-        <v>4.23687028884888</v>
+        <v>4.23686981201172</v>
       </c>
       <c r="H220" t="n">
         <v>4602</v>
@@ -6807,7 +6807,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>4.35189819335938</v>
+        <v>4.35189867019653</v>
       </c>
       <c r="H222" t="n">
         <v>699</v>
@@ -6981,7 +6981,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G228" t="n">
-        <v>4.24645566940308</v>
+        <v>4.24645614624023</v>
       </c>
       <c r="H228" t="n">
         <v>2110</v>
@@ -7039,7 +7039,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>4.66822576522827</v>
+        <v>4.66822528839111</v>
       </c>
       <c r="H230" t="n">
         <v>3934</v>
@@ -7155,7 +7155,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>5.46383666992188</v>
+        <v>5.46383714675903</v>
       </c>
       <c r="H234" t="n">
         <v>14646</v>
@@ -7184,7 +7184,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>5.55969429016113</v>
+        <v>5.55969476699829</v>
       </c>
       <c r="H235" t="n">
         <v>6682</v>
@@ -7358,7 +7358,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>5.84726428985596</v>
+        <v>5.84726476669312</v>
       </c>
       <c r="H241" t="n">
         <v>2099</v>
@@ -7387,7 +7387,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>5.55969429016113</v>
+        <v>5.55969476699829</v>
       </c>
       <c r="H242" t="n">
         <v>13513</v>
@@ -7416,7 +7416,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>5.84726428985596</v>
+        <v>5.84726476669312</v>
       </c>
       <c r="H243" t="n">
         <v>24106</v>
@@ -7445,7 +7445,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G244" t="n">
-        <v>5.84726428985596</v>
+        <v>5.84726476669312</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>5.84726428985596</v>
+        <v>5.84726476669312</v>
       </c>
       <c r="H251" t="n">
         <v>2337</v>
@@ -25982,6 +25982,35 @@
         <v>1675</v>
       </c>
       <c r="I883" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="s">
+        <v>9</v>
+      </c>
+      <c r="B884" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C884" t="n">
+        <v>7.46000003814697</v>
+      </c>
+      <c r="D884" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="E884" t="n">
+        <v>7.44000005722046</v>
+      </c>
+      <c r="F884" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="G884" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="H884" t="n">
+        <v>517</v>
+      </c>
+      <c r="I884" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -456,7 +456,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3517918586731</v>
+        <v>4.35179233551025</v>
       </c>
       <c r="H3" t="n">
         <v>12331</v>
@@ -543,7 +543,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G6" t="n">
-        <v>4.53351497650146</v>
+        <v>4.53351449966431</v>
       </c>
       <c r="H6" t="n">
         <v>82495</v>
@@ -601,7 +601,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G8" t="n">
-        <v>4.57177209854126</v>
+        <v>4.57177257537842</v>
       </c>
       <c r="H8" t="n">
         <v>1861</v>
@@ -630,7 +630,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G9" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H9" t="n">
         <v>4290</v>
@@ -659,7 +659,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G10" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H11" t="n">
         <v>8925</v>
@@ -717,7 +717,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H12" t="n">
         <v>3</v>
@@ -746,7 +746,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H13" t="n">
         <v>2000</v>
@@ -775,7 +775,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H14" t="n">
         <v>700</v>
@@ -862,7 +862,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>4.59090137481689</v>
+        <v>4.59090185165405</v>
       </c>
       <c r="H17" t="n">
         <v>19623</v>
@@ -978,7 +978,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H21" t="n">
         <v>1000</v>
@@ -1007,7 +1007,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G22" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H23" t="n">
         <v>400</v>
@@ -1065,7 +1065,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G24" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G25" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G31" t="n">
-        <v>4.38048458099365</v>
+        <v>4.38048505783081</v>
       </c>
       <c r="H31" t="n">
         <v>200</v>
@@ -1297,7 +1297,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G32" t="n">
-        <v>4.45700025558472</v>
+        <v>4.45699977874756</v>
       </c>
       <c r="H32" t="n">
         <v>2150</v>
@@ -1326,7 +1326,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G33" t="n">
-        <v>4.45700025558472</v>
+        <v>4.45699977874756</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>4.5</v>
       </c>
       <c r="G34" t="n">
-        <v>4.3039698600769</v>
+        <v>4.30396938323975</v>
       </c>
       <c r="H34" t="n">
         <v>2370</v>
@@ -1384,7 +1384,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>4.3517918586731</v>
+        <v>4.35179233551025</v>
       </c>
       <c r="H35" t="n">
         <v>2300</v>
@@ -1413,7 +1413,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G36" t="n">
-        <v>4.3517918586731</v>
+        <v>4.35179233551025</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>4.3517918586731</v>
+        <v>4.35179233551025</v>
       </c>
       <c r="H37" t="n">
         <v>9</v>
@@ -1471,7 +1471,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G38" t="n">
-        <v>4.3517918586731</v>
+        <v>4.35179233551025</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>4.39961338043213</v>
+        <v>4.39961385726929</v>
       </c>
       <c r="H39" t="n">
         <v>1250</v>
@@ -1529,7 +1529,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G40" t="n">
-        <v>4.38048458099365</v>
+        <v>4.38048505783081</v>
       </c>
       <c r="H40" t="n">
         <v>828</v>
@@ -1558,7 +1558,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>4.38048458099365</v>
+        <v>4.38048505783081</v>
       </c>
       <c r="H41" t="n">
         <v>200</v>
@@ -1761,7 +1761,7 @@
         <v>4.5</v>
       </c>
       <c r="G48" t="n">
-        <v>4.3039698600769</v>
+        <v>4.30396938323975</v>
       </c>
       <c r="H48" t="n">
         <v>50</v>
@@ -1848,7 +1848,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G51" t="n">
-        <v>4.37106990814209</v>
+        <v>4.37106943130493</v>
       </c>
       <c r="H51" t="n">
         <v>3376</v>
@@ -1906,7 +1906,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G53" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H53" t="n">
         <v>6000</v>
@@ -1935,7 +1935,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G54" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G66" t="n">
-        <v>4.42858362197876</v>
+        <v>4.42858409881592</v>
       </c>
       <c r="H66" t="n">
         <v>350</v>
@@ -2312,7 +2312,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>4.42858362197876</v>
+        <v>4.42858409881592</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>4.42858362197876</v>
+        <v>4.42858409881592</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>4.42858362197876</v>
+        <v>4.42858409881592</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G70" t="n">
-        <v>4.42858362197876</v>
+        <v>4.42858409881592</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G71" t="n">
-        <v>4.42858362197876</v>
+        <v>4.42858409881592</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G72" t="n">
-        <v>4.54361200332642</v>
+        <v>4.54361152648926</v>
       </c>
       <c r="H72" t="n">
         <v>2170</v>
@@ -2892,7 +2892,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G87" t="n">
-        <v>4.39024114608765</v>
+        <v>4.3902416229248</v>
       </c>
       <c r="H87" t="n">
         <v>500</v>
@@ -2921,7 +2921,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G88" t="n">
-        <v>4.39024114608765</v>
+        <v>4.3902416229248</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G120" t="n">
-        <v>4.37106990814209</v>
+        <v>4.37106943130493</v>
       </c>
       <c r="H120" t="n">
         <v>3050</v>
@@ -3878,7 +3878,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>4.37106990814209</v>
+        <v>4.37106943130493</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G144" t="n">
-        <v>4.08349990844727</v>
+        <v>4.08349943161011</v>
       </c>
       <c r="H144" t="n">
         <v>100</v>
@@ -4574,7 +4574,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G145" t="n">
-        <v>4.08349990844727</v>
+        <v>4.08349943161011</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>3.99722790718079</v>
+        <v>3.99722838401794</v>
       </c>
       <c r="H146" t="n">
         <v>1150</v>
@@ -4632,7 +4632,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G147" t="n">
-        <v>4.00681400299072</v>
+        <v>4.00681352615356</v>
       </c>
       <c r="H147" t="n">
         <v>10</v>
@@ -4661,7 +4661,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>4.00681400299072</v>
+        <v>4.00681352615356</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G150" t="n">
-        <v>4.23686981201172</v>
+        <v>4.23687028884888</v>
       </c>
       <c r="H150" t="n">
         <v>1292</v>
@@ -5154,7 +5154,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G165" t="n">
-        <v>4.02598476409912</v>
+        <v>4.02598524093628</v>
       </c>
       <c r="H165" t="n">
         <v>2701</v>
@@ -5676,7 +5676,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H183" t="n">
         <v>5513</v>
@@ -5937,7 +5937,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G192" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H192" t="n">
         <v>36</v>
@@ -6111,7 +6111,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H198" t="n">
         <v>5205</v>
@@ -6140,7 +6140,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G202" t="n">
-        <v>4.72573947906494</v>
+        <v>4.7257399559021</v>
       </c>
       <c r="H202" t="n">
         <v>41</v>
@@ -6285,7 +6285,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G204" t="n">
-        <v>4.78325414657593</v>
+        <v>4.78325366973877</v>
       </c>
       <c r="H204" t="n">
         <v>6987</v>
@@ -6372,7 +6372,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G207" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H207" t="n">
         <v>716</v>
@@ -6430,7 +6430,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G209" t="n">
-        <v>4.54361200332642</v>
+        <v>4.54361152648926</v>
       </c>
       <c r="H209" t="n">
         <v>6246</v>
@@ -6517,7 +6517,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G212" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H212" t="n">
         <v>13614</v>
@@ -6575,7 +6575,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G214" t="n">
-        <v>4.60112619400024</v>
+        <v>4.6011266708374</v>
       </c>
       <c r="H214" t="n">
         <v>304</v>
@@ -6720,7 +6720,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G219" t="n">
-        <v>4.32314157485962</v>
+        <v>4.32314205169678</v>
       </c>
       <c r="H219" t="n">
         <v>8285</v>
@@ -6749,7 +6749,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G220" t="n">
-        <v>4.23686981201172</v>
+        <v>4.23687028884888</v>
       </c>
       <c r="H220" t="n">
         <v>4602</v>
@@ -6807,7 +6807,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>4.35189867019653</v>
+        <v>4.35189819335938</v>
       </c>
       <c r="H222" t="n">
         <v>699</v>
@@ -6981,7 +6981,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G228" t="n">
-        <v>4.24645614624023</v>
+        <v>4.24645566940308</v>
       </c>
       <c r="H228" t="n">
         <v>2110</v>
@@ -7039,7 +7039,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>4.66822528839111</v>
+        <v>4.66822576522827</v>
       </c>
       <c r="H230" t="n">
         <v>3934</v>
@@ -7155,7 +7155,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>5.46383714675903</v>
+        <v>5.46383666992188</v>
       </c>
       <c r="H234" t="n">
         <v>14646</v>
@@ -7184,7 +7184,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>5.55969476699829</v>
+        <v>5.55969429016113</v>
       </c>
       <c r="H235" t="n">
         <v>6682</v>
@@ -7358,7 +7358,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>5.84726476669312</v>
+        <v>5.84726428985596</v>
       </c>
       <c r="H241" t="n">
         <v>2099</v>
@@ -7387,7 +7387,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>5.55969476699829</v>
+        <v>5.55969429016113</v>
       </c>
       <c r="H242" t="n">
         <v>13513</v>
@@ -7416,7 +7416,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>5.84726476669312</v>
+        <v>5.84726428985596</v>
       </c>
       <c r="H243" t="n">
         <v>24106</v>
@@ -7445,7 +7445,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G244" t="n">
-        <v>5.84726476669312</v>
+        <v>5.84726428985596</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>5.84726476669312</v>
+        <v>5.84726428985596</v>
       </c>
       <c r="H251" t="n">
         <v>2337</v>
@@ -26008,9 +26008,38 @@
         <v>7.65999984741211</v>
       </c>
       <c r="H884" t="n">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I884" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="s">
+        <v>9</v>
+      </c>
+      <c r="B885" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C885" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="D885" t="n">
+        <v>7.88000011444092</v>
+      </c>
+      <c r="E885" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="F885" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="G885" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="H885" t="n">
+        <v>5981</v>
+      </c>
+      <c r="I885" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G2" t="n">
-        <v>3.96347784996033</v>
+        <v>3.96347832679749</v>
       </c>
       <c r="H2" t="n">
         <v>19465</v>
@@ -456,7 +456,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G3" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H3" t="n">
         <v>12331</v>
@@ -485,7 +485,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>4.68654537200928</v>
+        <v>4.68654584884644</v>
       </c>
       <c r="H4" t="n">
         <v>18223</v>
@@ -543,7 +543,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G6" t="n">
-        <v>4.53351449966431</v>
+        <v>4.53351497650146</v>
       </c>
       <c r="H6" t="n">
         <v>82495</v>
@@ -804,7 +804,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G15" t="n">
-        <v>4.48569345474243</v>
+        <v>4.48569297790527</v>
       </c>
       <c r="H15" t="n">
         <v>1050</v>
@@ -833,7 +833,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G16" t="n">
-        <v>4.48569345474243</v>
+        <v>4.48569297790527</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G32" t="n">
-        <v>4.45699977874756</v>
+        <v>4.45700025558472</v>
       </c>
       <c r="H32" t="n">
         <v>2150</v>
@@ -1326,7 +1326,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G33" t="n">
-        <v>4.45699977874756</v>
+        <v>4.45700025558472</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>4.5</v>
       </c>
       <c r="G34" t="n">
-        <v>4.30396938323975</v>
+        <v>4.3039698600769</v>
       </c>
       <c r="H34" t="n">
         <v>2370</v>
@@ -1384,7 +1384,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H35" t="n">
         <v>2300</v>
@@ -1413,7 +1413,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G36" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H37" t="n">
         <v>9</v>
@@ -1471,7 +1471,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G38" t="n">
-        <v>4.35179233551025</v>
+        <v>4.3517918586731</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>4.5</v>
       </c>
       <c r="G48" t="n">
-        <v>4.30396938323975</v>
+        <v>4.3039698600769</v>
       </c>
       <c r="H48" t="n">
         <v>50</v>
@@ -26028,7 +26028,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="E885" t="n">
-        <v>7.65999984741211</v>
+        <v>7.59999990463257</v>
       </c>
       <c r="F885" t="n">
         <v>7.59999990463257</v>
@@ -26040,6 +26040,35 @@
         <v>5981</v>
       </c>
       <c r="I885" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="s">
+        <v>9</v>
+      </c>
+      <c r="B886" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C886" t="n">
+        <v>7.88000011444092</v>
+      </c>
+      <c r="D886" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="E886" t="n">
+        <v>7.73999977111816</v>
+      </c>
+      <c r="F886" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="G886" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="H886" t="n">
+        <v>1693</v>
+      </c>
+      <c r="I886" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G2" t="n">
-        <v>3.96347832679749</v>
+        <v>3.96347784996033</v>
       </c>
       <c r="H2" t="n">
         <v>19465</v>
@@ -485,7 +485,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>4.68654584884644</v>
+        <v>4.68654537200928</v>
       </c>
       <c r="H4" t="n">
         <v>18223</v>
@@ -804,7 +804,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G15" t="n">
-        <v>4.48569297790527</v>
+        <v>4.48569345474243</v>
       </c>
       <c r="H15" t="n">
         <v>1050</v>
@@ -833,7 +833,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G16" t="n">
-        <v>4.48569297790527</v>
+        <v>4.48569345474243</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>4.59090185165405</v>
+        <v>4.59090137481689</v>
       </c>
       <c r="H17" t="n">
         <v>19623</v>
@@ -1268,7 +1268,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G31" t="n">
-        <v>4.38048505783081</v>
+        <v>4.38048458099365</v>
       </c>
       <c r="H31" t="n">
         <v>200</v>
@@ -1297,7 +1297,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G32" t="n">
-        <v>4.45700025558472</v>
+        <v>4.45699977874756</v>
       </c>
       <c r="H32" t="n">
         <v>2150</v>
@@ -1326,7 +1326,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G33" t="n">
-        <v>4.45700025558472</v>
+        <v>4.45699977874756</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>4.5</v>
       </c>
       <c r="G34" t="n">
-        <v>4.3039698600769</v>
+        <v>4.30396938323975</v>
       </c>
       <c r="H34" t="n">
         <v>2370</v>
@@ -1529,7 +1529,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G40" t="n">
-        <v>4.38048505783081</v>
+        <v>4.38048458099365</v>
       </c>
       <c r="H40" t="n">
         <v>828</v>
@@ -1558,7 +1558,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>4.38048505783081</v>
+        <v>4.38048458099365</v>
       </c>
       <c r="H41" t="n">
         <v>200</v>
@@ -1761,7 +1761,7 @@
         <v>4.5</v>
       </c>
       <c r="G48" t="n">
-        <v>4.3039698600769</v>
+        <v>4.30396938323975</v>
       </c>
       <c r="H48" t="n">
         <v>50</v>
@@ -1848,7 +1848,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G51" t="n">
-        <v>4.37106943130493</v>
+        <v>4.37106990814209</v>
       </c>
       <c r="H51" t="n">
         <v>3376</v>
@@ -1906,7 +1906,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G53" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H53" t="n">
         <v>6000</v>
@@ -1935,7 +1935,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G54" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G66" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H66" t="n">
         <v>350</v>
@@ -2312,7 +2312,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G70" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G71" t="n">
-        <v>4.42858409881592</v>
+        <v>4.42858362197876</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G72" t="n">
-        <v>4.54361152648926</v>
+        <v>4.54361200332642</v>
       </c>
       <c r="H72" t="n">
         <v>2170</v>
@@ -2892,7 +2892,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G87" t="n">
-        <v>4.3902416229248</v>
+        <v>4.39024114608765</v>
       </c>
       <c r="H87" t="n">
         <v>500</v>
@@ -2921,7 +2921,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G88" t="n">
-        <v>4.3902416229248</v>
+        <v>4.39024114608765</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G120" t="n">
-        <v>4.37106943130493</v>
+        <v>4.37106990814209</v>
       </c>
       <c r="H120" t="n">
         <v>3050</v>
@@ -3878,7 +3878,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>4.37106943130493</v>
+        <v>4.37106990814209</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G144" t="n">
-        <v>4.08349943161011</v>
+        <v>4.08349990844727</v>
       </c>
       <c r="H144" t="n">
         <v>100</v>
@@ -4574,7 +4574,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G145" t="n">
-        <v>4.08349943161011</v>
+        <v>4.08349990844727</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>3.99722838401794</v>
+        <v>3.99722790718079</v>
       </c>
       <c r="H146" t="n">
         <v>1150</v>
@@ -4632,7 +4632,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G147" t="n">
-        <v>4.00681352615356</v>
+        <v>4.00681400299072</v>
       </c>
       <c r="H147" t="n">
         <v>10</v>
@@ -4661,7 +4661,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>4.00681352615356</v>
+        <v>4.00681400299072</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G150" t="n">
-        <v>4.23687028884888</v>
+        <v>4.23686981201172</v>
       </c>
       <c r="H150" t="n">
         <v>1292</v>
@@ -5154,7 +5154,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G165" t="n">
-        <v>4.02598524093628</v>
+        <v>4.02598476409912</v>
       </c>
       <c r="H165" t="n">
         <v>2701</v>
@@ -5676,7 +5676,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H183" t="n">
         <v>5513</v>
@@ -5937,7 +5937,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G192" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H192" t="n">
         <v>36</v>
@@ -6111,7 +6111,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H198" t="n">
         <v>5205</v>
@@ -6140,7 +6140,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G202" t="n">
-        <v>4.7257399559021</v>
+        <v>4.72573947906494</v>
       </c>
       <c r="H202" t="n">
         <v>41</v>
@@ -6285,7 +6285,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G204" t="n">
-        <v>4.78325366973877</v>
+        <v>4.78325414657593</v>
       </c>
       <c r="H204" t="n">
         <v>6987</v>
@@ -6372,7 +6372,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G207" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H207" t="n">
         <v>716</v>
@@ -6430,7 +6430,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G209" t="n">
-        <v>4.54361152648926</v>
+        <v>4.54361200332642</v>
       </c>
       <c r="H209" t="n">
         <v>6246</v>
@@ -6517,7 +6517,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G212" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H212" t="n">
         <v>13614</v>
@@ -6575,7 +6575,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G214" t="n">
-        <v>4.6011266708374</v>
+        <v>4.60112619400024</v>
       </c>
       <c r="H214" t="n">
         <v>304</v>
@@ -6720,7 +6720,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G219" t="n">
-        <v>4.32314205169678</v>
+        <v>4.32314157485962</v>
       </c>
       <c r="H219" t="n">
         <v>8285</v>
@@ -6749,7 +6749,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G220" t="n">
-        <v>4.23687028884888</v>
+        <v>4.23686981201172</v>
       </c>
       <c r="H220" t="n">
         <v>4602</v>
@@ -6807,7 +6807,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>4.35189819335938</v>
+        <v>4.35189867019653</v>
       </c>
       <c r="H222" t="n">
         <v>699</v>
@@ -6981,7 +6981,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G228" t="n">
-        <v>4.24645566940308</v>
+        <v>4.24645614624023</v>
       </c>
       <c r="H228" t="n">
         <v>2110</v>
@@ -7039,7 +7039,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>4.66822576522827</v>
+        <v>4.66822528839111</v>
       </c>
       <c r="H230" t="n">
         <v>3934</v>
@@ -7155,7 +7155,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>5.46383666992188</v>
+        <v>5.46383714675903</v>
       </c>
       <c r="H234" t="n">
         <v>14646</v>
@@ -7184,7 +7184,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>5.55969429016113</v>
+        <v>5.55969476699829</v>
       </c>
       <c r="H235" t="n">
         <v>6682</v>
@@ -7358,7 +7358,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>5.84726428985596</v>
+        <v>5.84726476669312</v>
       </c>
       <c r="H241" t="n">
         <v>2099</v>
@@ -7387,7 +7387,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>5.55969429016113</v>
+        <v>5.55969476699829</v>
       </c>
       <c r="H242" t="n">
         <v>13513</v>
@@ -7416,7 +7416,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>5.84726428985596</v>
+        <v>5.84726476669312</v>
       </c>
       <c r="H243" t="n">
         <v>24106</v>
@@ -7445,7 +7445,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G244" t="n">
-        <v>5.84726428985596</v>
+        <v>5.84726476669312</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>5.84726428985596</v>
+        <v>5.84726476669312</v>
       </c>
       <c r="H251" t="n">
         <v>2337</v>
@@ -26069,6 +26069,35 @@
         <v>1693</v>
       </c>
       <c r="I886" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="s">
+        <v>9</v>
+      </c>
+      <c r="B887" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C887" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="D887" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="E887" t="n">
+        <v>7.71999979019165</v>
+      </c>
+      <c r="F887" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="G887" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="H887" t="n">
+        <v>1702</v>
+      </c>
+      <c r="I887" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RES.MI.xlsx
+++ b/data/RES.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G2" t="n">
-        <v>3.96347784996033</v>
+        <v>3.96347832679749</v>
       </c>
       <c r="H2" t="n">
         <v>19465</v>
@@ -456,7 +456,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3517918586731</v>
+        <v>4.35179233551025</v>
       </c>
       <c r="H3" t="n">
         <v>12331</v>
@@ -485,7 +485,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>4.68654537200928</v>
+        <v>4.68654489517212</v>
       </c>
       <c r="H4" t="n">
         <v>18223</v>
@@ -514,7 +514,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G5" t="n">
-        <v>4.93521881103516</v>
+        <v>4.93521928787231</v>
       </c>
       <c r="H5" t="n">
         <v>6881</v>
@@ -543,7 +543,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G6" t="n">
-        <v>4.53351497650146</v>
+        <v>4.53351449966431</v>
       </c>
       <c r="H6" t="n">
         <v>82495</v>
@@ -601,7 +601,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G8" t="n">
-        <v>4.57177257537842</v>
+        <v>4.57177305221558</v>
       </c>
       <c r="H8" t="n">
         <v>1861</v>
@@ -804,7 +804,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G15" t="n">
-        <v>4.48569345474243</v>
+        <v>4.48569297790527</v>
       </c>
       <c r="H15" t="n">
         <v>1050</v>
@@ -833,7 +833,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G16" t="n">
-        <v>4.48569345474243</v>
+        <v>4.48569297790527</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G17" t="n">
-        <v>4.59090137481689</v>
+        <v>4.59090089797974</v>
       </c>
       <c r="H17" t="n">
         <v>19623</v>
@@ -891,7 +891,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G18" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H18" t="n">
         <v>14980</v>
@@ -1123,7 +1123,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G26" t="n">
-        <v>4.37092065811157</v>
+        <v>4.37092018127441</v>
       </c>
       <c r="H26" t="n">
         <v>2</v>
@@ -1268,7 +1268,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G31" t="n">
-        <v>4.38048458099365</v>
+        <v>4.38048505783081</v>
       </c>
       <c r="H31" t="n">
         <v>200</v>
@@ -1355,7 +1355,7 @@
         <v>4.5</v>
       </c>
       <c r="G34" t="n">
-        <v>4.30396938323975</v>
+        <v>4.3039698600769</v>
       </c>
       <c r="H34" t="n">
         <v>2370</v>
@@ -1384,7 +1384,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>4.3517918586731</v>
+        <v>4.35179233551025</v>
       </c>
       <c r="H35" t="n">
         <v>2300</v>
@@ -1413,7 +1413,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G36" t="n">
-        <v>4.3517918586731</v>
+        <v>4.35179233551025</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>4.3517918586731</v>
+        <v>4.35179233551025</v>
       </c>
       <c r="H37" t="n">
         <v>9</v>
@@ -1471,7 +1471,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G38" t="n">
-        <v>4.3517918586731</v>
+        <v>4.35179233551025</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G40" t="n">
-        <v>4.38048458099365</v>
+        <v>4.38048505783081</v>
       </c>
       <c r="H40" t="n">
         <v>828</v>
@@ -1558,7 +1558,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>4.38048458099365</v>
+        <v>4.38048505783081</v>
       </c>
       <c r="H41" t="n">
         <v>200</v>
@@ -1587,7 +1587,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G42" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H42" t="n">
         <v>3345</v>
@@ -1616,7 +1616,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G45" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G47" t="n">
-        <v>4.49525737762451</v>
+        <v>4.49525690078735</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>4.5</v>
       </c>
       <c r="G48" t="n">
-        <v>4.30396938323975</v>
+        <v>4.3039698600769</v>
       </c>
       <c r="H48" t="n">
         <v>50</v>
@@ -1790,7 +1790,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>4.27521276473999</v>
+        <v>4.27521324157715</v>
       </c>
       <c r="H49" t="n">
         <v>570</v>
@@ -1819,7 +1819,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G50" t="n">
-        <v>4.27521276473999</v>
+        <v>4.27521324157715</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G51" t="n">
-        <v>4.37106990814209</v>
+        <v>4.37106943130493</v>
       </c>
       <c r="H51" t="n">
         <v>3376</v>
@@ -2225,7 +2225,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G64" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H64" t="n">
         <v>250</v>
@@ -2254,7 +2254,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H65" t="n">
         <v>100</v>
@@ -2457,7 +2457,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G72" t="n">
-        <v>4.54361200332642</v>
+        <v>4.54361152648926</v>
       </c>
       <c r="H72" t="n">
         <v>2170</v>
@@ -2544,7 +2544,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H75" t="n">
         <v>560</v>
@@ -2573,7 +2573,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G78" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H78" t="n">
         <v>2000</v>
@@ -2718,7 +2718,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G81" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H81" t="n">
         <v>40</v>
@@ -2747,7 +2747,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G82" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G83" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G115" t="n">
-        <v>4.14101362228394</v>
+        <v>4.14101409912109</v>
       </c>
       <c r="H115" t="n">
         <v>60</v>
@@ -3733,7 +3733,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G116" t="n">
-        <v>4.14101362228394</v>
+        <v>4.14101409912109</v>
       </c>
       <c r="H116" t="n">
         <v>500</v>
@@ -3762,7 +3762,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G117" t="n">
-        <v>4.14101362228394</v>
+        <v>4.14101409912109</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G120" t="n">
-        <v>4.37106990814209</v>
+        <v>4.37106943130493</v>
       </c>
       <c r="H120" t="n">
         <v>3050</v>
@@ -3878,7 +3878,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>4.37106990814209</v>
+        <v>4.37106943130493</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H125" t="n">
         <v>750</v>
@@ -4023,7 +4023,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G126" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H129" t="n">
         <v>30</v>
@@ -4139,7 +4139,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G130" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>4.5</v>
       </c>
       <c r="G131" t="n">
-        <v>4.3135552406311</v>
+        <v>4.31355571746826</v>
       </c>
       <c r="H131" t="n">
         <v>840</v>
@@ -4197,7 +4197,7 @@
         <v>4.5</v>
       </c>
       <c r="G132" t="n">
-        <v>4.3135552406311</v>
+        <v>4.31355571746826</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>4.25</v>
       </c>
       <c r="G142" t="n">
-        <v>4.07391357421875</v>
+        <v>4.07391405105591</v>
       </c>
       <c r="H142" t="n">
         <v>2650</v>
@@ -4516,7 +4516,7 @@
         <v>4.25</v>
       </c>
       <c r="G143" t="n">
-        <v>4.07391357421875</v>
+        <v>4.07391405105591</v>
       </c>
       <c r="H143" t="n">
         <v>1000</v>
@@ -4603,7 +4603,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>3.99722790718079</v>
+        <v>3.99722838401794</v>
       </c>
       <c r="H146" t="n">
         <v>1150</v>
@@ -4632,7 +4632,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G147" t="n">
-        <v>4.00681400299072</v>
+        <v>4.00681352615356</v>
       </c>
       <c r="H147" t="n">
         <v>10</v>
@@ -4661,7 +4661,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>4.00681400299072</v>
+        <v>4.00681352615356</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G150" t="n">
-        <v>4.23686981201172</v>
+        <v>4.23687028884888</v>
       </c>
       <c r="H150" t="n">
         <v>1292</v>
@@ -5154,7 +5154,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G165" t="n">
-        <v>4.02598476409912</v>
+        <v>4.02598524093628</v>
       </c>
       <c r="H165" t="n">
         <v>2701</v>
@@ -5589,7 +5589,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>4.74491119384766</v>
+        <v>4.7449107170105</v>
       </c>
       <c r="H180" t="n">
         <v>3483</v>
@@ -5618,7 +5618,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G181" t="n">
-        <v>4.74491119384766</v>
+        <v>4.7449107170105</v>
       </c>
       <c r="H181" t="n">
         <v>1342</v>
@@ -5734,7 +5734,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G185" t="n">
-        <v>4.4956841468811</v>
+        <v>4.49568319320679</v>
       </c>
       <c r="H185" t="n">
         <v>1100</v>
@@ -5763,7 +5763,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G186" t="n">
-        <v>4.4956841468811</v>
+        <v>4.49568319320679</v>
       </c>
       <c r="H186" t="n">
         <v>150</v>
@@ -5908,7 +5908,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G191" t="n">
-        <v>4.64905405044556</v>
+        <v>4.64905452728271</v>
       </c>
       <c r="H191" t="n">
         <v>2900</v>
@@ -6024,7 +6024,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H195" t="n">
         <v>858</v>
@@ -6053,7 +6053,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G196" t="n">
-        <v>4.45734071731567</v>
+        <v>4.45734119415283</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G197" t="n">
-        <v>4.44775485992432</v>
+        <v>4.44775533676147</v>
       </c>
       <c r="H197" t="n">
         <v>7251</v>
@@ -6169,7 +6169,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G200" t="n">
-        <v>4.68739700317383</v>
+        <v>4.68739652633667</v>
       </c>
       <c r="H200" t="n">
         <v>2449</v>
@@ -6285,7 +6285,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G204" t="n">
-        <v>4.78325414657593</v>
+        <v>4.78325366973877</v>
       </c>
       <c r="H204" t="n">
         <v>6987</v>
@@ -6314,7 +6314,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G205" t="n">
-        <v>4.64905405044556</v>
+        <v>4.64905452728271</v>
       </c>
       <c r="H205" t="n">
         <v>6218</v>
@@ -6430,7 +6430,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G209" t="n">
-        <v>4.54361200332642</v>
+        <v>4.54361152648926</v>
       </c>
       <c r="H209" t="n">
         <v>6246</v>
@@ -6488,7 +6488,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>4.64905405044556</v>
+        <v>4.64905452728271</v>
       </c>
       <c r="H211" t="n">
         <v>3534</v>
@@ -6604,7 +6604,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G215" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H215" t="n">
         <v>4174</v>
@@ -6633,7 +6633,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>4.4956841468811</v>
+        <v>4.49568319320679</v>
       </c>
       <c r="H216" t="n">
         <v>3969</v>
@@ -6662,7 +6662,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G217" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H217" t="n">
         <v>5</v>
@@ -6691,7 +6691,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G218" t="n">
-        <v>4.4956841468811</v>
+        <v>4.49568319320679</v>
       </c>
       <c r="H218" t="n">
         <v>553</v>
@@ -6749,7 +6749,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G220" t="n">
-        <v>4.23686981201172</v>
+        <v>4.23687028884888</v>
       </c>
       <c r="H220" t="n">
         <v>4602</v>
@@ -6807,7 +6807,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>4.35189867019653</v>
+        <v>4.35189819335938</v>
       </c>
       <c r="H222" t="n">
         <v>699</v>
@@ -6836,7 +6836,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G223" t="n">
-        <v>4.4956841468811</v>
+        <v>4.49568319320679</v>
       </c>
       <c r="H223" t="n">
         <v>3084</v>
@@ -6865,7 +6865,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H224" t="n">
         <v>2536</v>
@@ -6894,7 +6894,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G225" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H225" t="n">
         <v>2200</v>
@@ -6923,7 +6923,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G227" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G228" t="n">
-        <v>4.24645614624023</v>
+        <v>4.24645566940308</v>
       </c>
       <c r="H228" t="n">
         <v>2110</v>
@@ -7010,7 +7010,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G229" t="n">
-        <v>4.50526905059814</v>
+        <v>4.50526857376099</v>
       </c>
       <c r="H229" t="n">
         <v>600</v>
@@ -7097,7 +7097,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G232" t="n">
-        <v>4.74491119384766</v>
+        <v>4.7449107170105</v>
       </c>
       <c r="H232" t="n">
         <v>4566</v>
@@ -7126,7 +7126,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G233" t="n">
-        <v>5.02289533615112</v>
+        <v>5.02289581298828</v>
       </c>
       <c r="H233" t="n">
         <v>1155</v>
@@ -7184,7 +7184,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>5.55969476699829</v>
+        <v>5.55969381332397</v>
       </c>
       <c r="H235" t="n">
         <v>6682</v>
@@ -7213,7 +7213,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G236" t="n">
-        <v>5.6076226234436</v>
+        <v>5.60762214660645</v>
       </c>
       <c r="H236" t="n">
         <v>13254</v>
@@ -7242,7 +7242,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>5.6076226234436</v>
+        <v>5.60762214660645</v>
       </c>
       <c r="H237" t="n">
         <v>4716</v>
@@ -7329,7 +7329,7 @@
         <v>6</v>
       </c>
       <c r="G240" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H240" t="n">
         <v>2874</v>
@@ -7358,7 +7358,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>5.84726476669312</v>
+        <v>5.8472638130188</v>
       </c>
       <c r="H241" t="n">
         <v>2099</v>
@@ -7387,7 +7387,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>5.55969476699829</v>
+        <v>5.55969381332397</v>
       </c>
       <c r="H242" t="n">
         <v>13513</v>
@@ -7416,7 +7416,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>5.84726476669312</v>
+        <v>5.8472638130188</v>
       </c>
       <c r="H243" t="n">
         <v>24106</v>
@@ -7445,7 +7445,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G244" t="n">
-        <v>5.84726476669312</v>
+        <v>5.8472638130188</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>6</v>
       </c>
       <c r="G249" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H249" t="n">
         <v>1</v>
@@ -7648,7 +7648,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>5.84726476669312</v>
+        <v>5.8472638130188</v>
       </c>
       <c r="H251" t="n">
         <v>2337</v>
@@ -7677,7 +7677,7 @@
         <v>6.25</v>
       </c>
       <c r="G252" t="n">
-        <v>5.99104976654053</v>
+        <v>5.99104928970337</v>
       </c>
       <c r="H252" t="n">
         <v>2848</v>
@@ -7735,7 +7735,7 @@
         <v>6</v>
       </c>
       <c r="G254" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H254" t="n">
         <v>6926</v>
@@ -7822,7 +7822,7 @@
         <v>6</v>
       </c>
       <c r="G257" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H257" t="n">
         <v>180</v>
@@ -7851,7 +7851,7 @@
         <v>6</v>
       </c>
       <c r="G258" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H258" t="n">
         <v>100</v>
@@ -7880,7 +7880,7 @@
         <v>6</v>
       </c>
       <c r="G259" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H259" t="n">
         <v>8795</v>
@@ -7909,7 +7909,7 @@
         <v>6</v>
       </c>
       <c r="G260" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H260" t="n">
         <v>2800</v>
@@ -7938,7 +7938,7 @@
         <v>6</v>
       </c>
       <c r="G261" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H261" t="n">
         <v>5000</v>
@@ -7967,7 +7967,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>5.70347929000854</v>
+        <v>5.70347881317139</v>
       </c>
       <c r="H262" t="n">
         <v>1549</v>
@@ -7996,7 +7996,7 @@
         <v>6</v>
       </c>
       <c r="G263" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H263" t="n">
         <v>175</v>
@@ -8025,7 +8025,7 @@
         <v>6</v>
       </c>
       <c r="G264" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H264" t="n">
         <v>300</v>
@@ -8054,7 +8054,7 @@
         <v>6</v>
       </c>
       <c r="G265" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>6</v>
       </c>
       <c r="G266" t="n">
-        <v>5.75140762329102</v>
+        <v>5.75140714645386</v>
       </c>
       <c r="H266" t="n">
         <v>50</v>
@@ -9011,7 +9011,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>5.90632772445679</v>
+        <v>5.90632724761963</v>
       </c>
       <c r="H298" t="n">
         <v>6072</v>
@@ -9098,7 +9098,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G301" t="n">
-        <v>5.66426515579224</v>
+        <v>5.66426467895508</v>
       </c>
       <c r="H301" t="n">
         <v>4731</v>
@@ -9127,7 +9127,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G302" t="n">
-        <v>5.66426515579224</v>
+        <v>5.66426467895508</v>
       </c>
       <c r="H302" t="n">
         <v>6123</v>
@@ -9156,7 +9156,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>5.66426515579224</v>
+        <v>5.66426467895508</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>5.66426515579224</v>
+        <v>5.66426467895508</v>
       </c>
       <c r="H305" t="n">
         <v>1</v>
@@ -9243,7 +9243,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G306" t="n">
-        <v>5.61585283279419</v>
+        <v>5.61585235595703</v>
       </c>
       <c r="H306" t="n">
         <v>1509</v>
@@ -9678,7 +9678,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>5.61585283279419</v>
+        <v>5.61585235595703</v>
       </c>
       <c r="H321" t="n">
         <v>2211</v>
@@ -9707,7 +9707,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>5.61585283279419</v>
+        <v>5.61585235595703</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>5.75</v>
       </c>
       <c r="G323" t="n">
-        <v>5.56743955612183</v>
+        <v>5.56744003295898</v>
       </c>
       <c r="H323" t="n">
         <v>1058</v>
@@ -9939,7 +9939,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>5.61585283279419</v>
+        <v>5.61585235595703</v>
       </c>
       <c r="H330" t="n">
         <v>3754</v>
@@ -10374,7 +10374,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>5.61585283279419</v>
+        <v>5.61585235595703</v>
       </c>
       <c r="H345" t="n">
         <v>2400</v>
@@ -10432,7 +10432,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G347" t="n">
-        <v>6.14838981628418</v>
+        <v>6.14839029312134</v>
       </c>
       <c r="H347" t="n">
         <v>37832</v>
@@ -10490,7 +10490,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G349" t="n">
-        <v>7.45552778244019</v>
+        <v>7.45552825927734</v>
       </c>
       <c r="H349" t="n">
         <v>12938</v>
@@ -10751,7 +10751,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G358" t="n">
-        <v>8.61742782592773</v>
+        <v>8.61742877960205</v>
       </c>
       <c r="H358" t="n">
         <v>3309</v>
@@ -10780,7 +10780,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G359" t="n">
-        <v>8.76266670227051</v>
+        <v>8.76266574859619</v>
       </c>
       <c r="H359" t="n">
         <v>4060</v>
@@ -10867,7 +10867,7 @@
         <v>9.75</v>
       </c>
       <c r="G362" t="n">
-        <v>9.4404411315918</v>
+        <v>9.44044208526611</v>
       </c>
       <c r="H362" t="n">
         <v>3792</v>
@@ -10896,7 +10896,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G363" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H363" t="n">
         <v>6251</v>
@@ -10925,7 +10925,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>10.5539283752441</v>
+        <v>10.5539293289185</v>
       </c>
       <c r="H364" t="n">
         <v>5314</v>
@@ -11041,7 +11041,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G368" t="n">
-        <v>11.8126554489136</v>
+        <v>11.8126544952393</v>
       </c>
       <c r="H368" t="n">
         <v>3457</v>
@@ -11128,7 +11128,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G371" t="n">
-        <v>11.8126554489136</v>
+        <v>11.8126544952393</v>
       </c>
       <c r="H371" t="n">
         <v>1348</v>
@@ -11273,7 +11273,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G376" t="n">
-        <v>11.3285303115845</v>
+        <v>11.3285293579102</v>
       </c>
       <c r="H376" t="n">
         <v>1130</v>
@@ -11418,7 +11418,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>11.2317056655884</v>
+        <v>11.2317047119141</v>
       </c>
       <c r="H381" t="n">
         <v>2882</v>
@@ -11737,7 +11737,7 @@
         <v>10</v>
       </c>
       <c r="G392" t="n">
-        <v>9.68250465393066</v>
+        <v>9.68250370025635</v>
       </c>
       <c r="H392" t="n">
         <v>3005</v>
@@ -11853,7 +11853,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G396" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H396" t="n">
         <v>415</v>
@@ -11911,7 +11911,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G398" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H398" t="n">
         <v>12</v>
@@ -11969,7 +11969,7 @@
         <v>10</v>
       </c>
       <c r="G400" t="n">
-        <v>9.68250465393066</v>
+        <v>9.68250370025635</v>
       </c>
       <c r="H400" t="n">
         <v>60</v>
@@ -11998,7 +11998,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G401" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H401" t="n">
         <v>1390</v>
@@ -12027,7 +12027,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G402" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H402" t="n">
         <v>200</v>
@@ -12056,7 +12056,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H403" t="n">
         <v>94</v>
@@ -12085,7 +12085,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G404" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H404" t="n">
         <v>5</v>
@@ -12114,7 +12114,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G405" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H405" t="n">
         <v>126</v>
@@ -12375,7 +12375,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G414" t="n">
-        <v>9.05314159393311</v>
+        <v>9.05314254760742</v>
       </c>
       <c r="H414" t="n">
         <v>1125</v>
@@ -12404,7 +12404,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G415" t="n">
-        <v>9.05314159393311</v>
+        <v>9.05314254760742</v>
       </c>
       <c r="H415" t="n">
         <v>1982</v>
@@ -12433,7 +12433,7 @@
         <v>9.25</v>
       </c>
       <c r="G416" t="n">
-        <v>8.9563159942627</v>
+        <v>8.95631694793701</v>
       </c>
       <c r="H416" t="n">
         <v>71</v>
@@ -12665,7 +12665,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G424" t="n">
-        <v>9.58567905426025</v>
+        <v>9.58567810058594</v>
       </c>
       <c r="H424" t="n">
         <v>1554</v>
@@ -12752,7 +12752,7 @@
         <v>9.75</v>
       </c>
       <c r="G427" t="n">
-        <v>9.4404411315918</v>
+        <v>9.44044208526611</v>
       </c>
       <c r="H427" t="n">
         <v>264</v>
@@ -12897,7 +12897,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>9.10155391693115</v>
+        <v>9.10155296325684</v>
       </c>
       <c r="H432" t="n">
         <v>1636</v>
@@ -13129,7 +13129,7 @@
         <v>7.5</v>
       </c>
       <c r="G440" t="n">
-        <v>7.26187801361084</v>
+        <v>7.261878490448</v>
       </c>
       <c r="H440" t="n">
         <v>3612</v>
@@ -13158,7 +13158,7 @@
         <v>7.5</v>
       </c>
       <c r="G441" t="n">
-        <v>7.26187801361084</v>
+        <v>7.261878490448</v>
       </c>
       <c r="H441" t="n">
         <v>2382</v>
@@ -13187,7 +13187,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G442" t="n">
-        <v>6.87457799911499</v>
+        <v>6.87457752227783</v>
       </c>
       <c r="H442" t="n">
         <v>4692</v>
@@ -13390,7 +13390,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G449" t="n">
-        <v>6.09997749328613</v>
+        <v>6.09997797012329</v>
       </c>
       <c r="H449" t="n">
         <v>15040</v>
@@ -13419,7 +13419,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G450" t="n">
-        <v>6.14838981628418</v>
+        <v>6.14839029312134</v>
       </c>
       <c r="H450" t="n">
         <v>2310</v>
@@ -13448,7 +13448,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G451" t="n">
-        <v>6.09997749328613</v>
+        <v>6.09997797012329</v>
       </c>
       <c r="H451" t="n">
         <v>2158</v>
@@ -13477,7 +13477,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G452" t="n">
-        <v>6.14838981628418</v>
+        <v>6.14839029312134</v>
       </c>
       <c r="H452" t="n">
         <v>2258</v>
@@ -13506,7 +13506,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G453" t="n">
-        <v>6.09997749328613</v>
+        <v>6.09997797012329</v>
       </c>
       <c r="H453" t="n">
         <v>2163</v>
@@ -13535,7 +13535,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>5.90632772445679</v>
+        <v>5.90632724761963</v>
       </c>
       <c r="H454" t="n">
         <v>7331</v>
@@ -13651,7 +13651,7 @@
         <v>6.25</v>
       </c>
       <c r="G458" t="n">
-        <v>6.05156517028809</v>
+        <v>6.05156469345093</v>
       </c>
       <c r="H458" t="n">
         <v>11592</v>
@@ -13825,7 +13825,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G464" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H464" t="n">
         <v>2932</v>
@@ -13854,7 +13854,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H465" t="n">
         <v>2363</v>
@@ -13970,7 +13970,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G469" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H469" t="n">
         <v>9476</v>
@@ -13999,7 +13999,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G470" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H470" t="n">
         <v>2002</v>
@@ -14028,7 +14028,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G471" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H471" t="n">
         <v>2709</v>
@@ -14144,7 +14144,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G475" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H475" t="n">
         <v>1903</v>
@@ -14173,7 +14173,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>6.63251495361328</v>
+        <v>6.63251543045044</v>
       </c>
       <c r="H476" t="n">
         <v>1150</v>
@@ -14579,7 +14579,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G490" t="n">
-        <v>6.39045238494873</v>
+        <v>6.39045286178589</v>
       </c>
       <c r="H490" t="n">
         <v>6956</v>
@@ -14608,7 +14608,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G491" t="n">
-        <v>6.39045238494873</v>
+        <v>6.39045286178589</v>
       </c>
       <c r="H491" t="n">
         <v>25262</v>
@@ -14695,7 +14695,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G494" t="n">
-        <v>6.39045238494873</v>
+        <v>6.39045286178589</v>
       </c>
       <c r="H494" t="n">
         <v>5635</v>
@@ -14753,7 +14753,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G496" t="n">
-        <v>6.50664234161377</v>
+        <v>6.50664281845093</v>
       </c>
       <c r="H496" t="n">
         <v>1359</v>
@@ -14782,7 +14782,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G497" t="n">
-        <v>6.48727798461914</v>
+        <v>6.48727750778198</v>
       </c>
       <c r="H497" t="n">
         <v>200</v>
@@ -14811,7 +14811,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G498" t="n">
-        <v>6.48727798461914</v>
+        <v>6.48727750778198</v>
       </c>
       <c r="H498" t="n">
         <v>14931</v>
@@ -14840,7 +14840,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G499" t="n">
-        <v>6.48727798461914</v>
+        <v>6.48727750778198</v>
       </c>
       <c r="H499" t="n">
         <v>502</v>
@@ -14869,7 +14869,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G500" t="n">
-        <v>6.56473779678345</v>
+        <v>6.56473827362061</v>
       </c>
       <c r="H500" t="n">
         <v>101</v>
@@ -14898,7 +14898,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G501" t="n">
-        <v>6.56473779678345</v>
+        <v>6.56473827362061</v>
       </c>
       <c r="H501" t="n">
         <v>1073</v>
@@ -14927,7 +14927,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G502" t="n">
-        <v>6.56473779678345</v>
+        <v>6.56473827362061</v>
       </c>
       <c r="H502" t="n">
         <v>678</v>
@@ -15014,7 +15014,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>6.73902320861816</v>
+        <v>6.73902273178101</v>
       </c>
       <c r="H505" t="n">
         <v>795</v>
@@ -15159,7 +15159,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G510" t="n">
-        <v>6.48727798461914</v>
+        <v>6.48727750778198</v>
       </c>
       <c r="H510" t="n">
         <v>3139</v>
@@ -15188,7 +15188,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G511" t="n">
-        <v>6.56473779678345</v>
+        <v>6.56473827362061</v>
       </c>
       <c r="H511" t="n">
         <v>2377</v>
@@ -26098,6 +26098,35 @@
         <v>1702</v>
       </c>
       <c r="I887" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="s">
+        <v>9</v>
+      </c>
+      <c r="B888" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C888" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="D888" t="n">
+        <v>7.88000011444092</v>
+      </c>
+      <c r="E888" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="F888" t="n">
+        <v>7.88000011444092</v>
+      </c>
+      <c r="G888" t="n">
+        <v>7.88000011444092</v>
+      </c>
+      <c r="H888" t="n">
+        <v>201</v>
+      </c>
+      <c r="I888" t="s">
         <v>9</v>
       </c>
     </row>
